--- a/templates/quickval_template.xlsx
+++ b/templates/quickval_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sammiller/Desktop/Mesirow/OMreader/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{554CB0C0-D24B-E54E-8A59-2855B985B09A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{794E917A-403A-7244-B950-D902F907E379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="1" xr2:uid="{401FEA37-EBEB-4370-B91A-5CF478EDB23C}"/>
+    <workbookView xWindow="-37360" yWindow="500" windowWidth="37360" windowHeight="21100" activeTab="1" xr2:uid="{401FEA37-EBEB-4370-B91A-5CF478EDB23C}"/>
   </bookViews>
   <sheets>
     <sheet name="Validation Lists | Graph Values" sheetId="4" state="hidden" r:id="rId1"/>
@@ -2050,7 +2050,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="303">
+  <cellXfs count="301">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2716,6 +2716,33 @@
     <xf numFmtId="10" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="5" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="39" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="5" fontId="22" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="39" fontId="22" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="5" fontId="22" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="39" fontId="22" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="39" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2736,35 +2763,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="5" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="39" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="5" fontId="22" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="39" fontId="22" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="5" fontId="22" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="39" fontId="22" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="39" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -4790,44 +4788,44 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="286" t="str">
+      <c r="B2" s="297" t="str">
         <f>CONCATENATE(C5," | ","Quick Valuation")</f>
         <v xml:space="preserve"> | Quick Valuation</v>
       </c>
-      <c r="C2" s="286"/>
-      <c r="D2" s="286"/>
-      <c r="E2" s="286"/>
-      <c r="F2" s="286"/>
-      <c r="G2" s="286"/>
-      <c r="H2" s="286"/>
-      <c r="I2" s="286"/>
-      <c r="J2" s="286"/>
-      <c r="K2" s="286"/>
-      <c r="L2" s="286"/>
-      <c r="M2" s="286"/>
-      <c r="N2" s="286"/>
-      <c r="O2" s="286"/>
-      <c r="P2" s="286"/>
-      <c r="Q2" s="286"/>
-      <c r="R2" s="286"/>
-      <c r="S2" s="286"/>
+      <c r="C2" s="297"/>
+      <c r="D2" s="297"/>
+      <c r="E2" s="297"/>
+      <c r="F2" s="297"/>
+      <c r="G2" s="297"/>
+      <c r="H2" s="297"/>
+      <c r="I2" s="297"/>
+      <c r="J2" s="297"/>
+      <c r="K2" s="297"/>
+      <c r="L2" s="297"/>
+      <c r="M2" s="297"/>
+      <c r="N2" s="297"/>
+      <c r="O2" s="297"/>
+      <c r="P2" s="297"/>
+      <c r="Q2" s="297"/>
+      <c r="R2" s="297"/>
+      <c r="S2" s="297"/>
     </row>
     <row r="3" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="280">
         <f ca="1">TODAY()</f>
         <v>46136</v>
       </c>
-      <c r="R3" s="287">
+      <c r="R3" s="298">
         <v>5</v>
       </c>
-      <c r="S3" s="287"/>
+      <c r="S3" s="298"/>
     </row>
     <row r="4" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="283" t="s">
+      <c r="B4" s="294" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="284"/>
-      <c r="F4" s="291" t="s">
+      <c r="C4" s="295"/>
+      <c r="F4" s="284" t="s">
         <v>93</v>
       </c>
       <c r="G4" s="94" t="s">
@@ -4895,10 +4893,10 @@
       <c r="U5" s="99" t="s">
         <v>271</v>
       </c>
-      <c r="V5" s="292">
+      <c r="V5" s="285">
         <v>95000</v>
       </c>
-      <c r="W5" s="293">
+      <c r="W5" s="286">
         <v>0</v>
       </c>
       <c r="X5" s="100">
@@ -4948,10 +4946,10 @@
       <c r="U6" s="99" t="s">
         <v>272</v>
       </c>
-      <c r="V6" s="292">
+      <c r="V6" s="285">
         <v>65000</v>
       </c>
-      <c r="W6" s="293">
+      <c r="W6" s="286">
         <v>0</v>
       </c>
       <c r="X6" s="100">
@@ -5010,10 +5008,10 @@
       <c r="U7" s="99" t="s">
         <v>273</v>
       </c>
-      <c r="V7" s="292">
+      <c r="V7" s="285">
         <v>55000</v>
       </c>
-      <c r="W7" s="293">
+      <c r="W7" s="286">
         <v>0</v>
       </c>
       <c r="X7" s="100">
@@ -5072,10 +5070,10 @@
       <c r="U8" s="99" t="s">
         <v>274</v>
       </c>
-      <c r="V8" s="292">
+      <c r="V8" s="285">
         <v>50000</v>
       </c>
-      <c r="W8" s="293">
+      <c r="W8" s="286">
         <v>0</v>
       </c>
       <c r="X8" s="100">
@@ -5134,10 +5132,10 @@
       <c r="U9" s="110" t="s">
         <v>275</v>
       </c>
-      <c r="V9" s="294">
+      <c r="V9" s="287">
         <v>50000</v>
       </c>
-      <c r="W9" s="295">
+      <c r="W9" s="288">
         <v>0</v>
       </c>
       <c r="X9" s="111">
@@ -5199,10 +5197,10 @@
       <c r="U10" s="99" t="s">
         <v>276</v>
       </c>
-      <c r="V10" s="292">
+      <c r="V10" s="285">
         <v>75000</v>
       </c>
-      <c r="W10" s="293">
+      <c r="W10" s="286">
         <v>0</v>
       </c>
       <c r="X10" s="100">
@@ -5260,10 +5258,10 @@
       <c r="U11" s="99" t="s">
         <v>277</v>
       </c>
-      <c r="V11" s="292">
+      <c r="V11" s="285">
         <v>55000</v>
       </c>
-      <c r="W11" s="293">
+      <c r="W11" s="286">
         <v>0</v>
       </c>
       <c r="X11" s="100">
@@ -5321,10 +5319,10 @@
       <c r="U12" s="99" t="s">
         <v>278</v>
       </c>
-      <c r="V12" s="292">
+      <c r="V12" s="285">
         <v>45000</v>
       </c>
-      <c r="W12" s="293">
+      <c r="W12" s="286">
         <v>0</v>
       </c>
       <c r="X12" s="100">
@@ -5385,10 +5383,10 @@
       <c r="U13" s="99" t="s">
         <v>279</v>
       </c>
-      <c r="V13" s="292">
+      <c r="V13" s="285">
         <v>35000</v>
       </c>
-      <c r="W13" s="293">
+      <c r="W13" s="286">
         <v>0</v>
       </c>
       <c r="X13" s="100">
@@ -5446,10 +5444,10 @@
       <c r="U14" s="119" t="s">
         <v>280</v>
       </c>
-      <c r="V14" s="296">
+      <c r="V14" s="289">
         <v>50000</v>
       </c>
-      <c r="W14" s="297">
+      <c r="W14" s="290">
         <v>0</v>
       </c>
       <c r="X14" s="120">
@@ -5508,8 +5506,7 @@
       <c r="U15" s="121" t="s">
         <v>281</v>
       </c>
-      <c r="V15" s="298"/>
-      <c r="W15" s="299">
+      <c r="W15" s="291">
         <f>SUM(W5:W14)</f>
         <v>0</v>
       </c>
@@ -5569,8 +5566,7 @@
       <c r="U16" s="99" t="s">
         <v>288</v>
       </c>
-      <c r="V16" s="298"/>
-      <c r="W16" s="300">
+      <c r="W16" s="292">
         <v>0.12</v>
       </c>
       <c r="X16" s="100">
@@ -5599,8 +5595,8 @@
       <c r="U17" s="119" t="s">
         <v>282</v>
       </c>
-      <c r="V17" s="301"/>
-      <c r="W17" s="302">
+      <c r="V17" s="127"/>
+      <c r="W17" s="293">
         <v>0.28000000000000003</v>
       </c>
       <c r="X17" s="120">
@@ -5732,10 +5728,10 @@
       </c>
     </row>
     <row r="20" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="283" t="s">
+      <c r="B20" s="294" t="s">
         <v>107</v>
       </c>
-      <c r="C20" s="284"/>
+      <c r="C20" s="295"/>
       <c r="E20" s="105" t="s">
         <v>52</v>
       </c>
@@ -5828,20 +5824,20 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U21" s="283" t="s">
+      <c r="U21" s="294" t="s">
         <v>300</v>
       </c>
-      <c r="V21" s="285"/>
-      <c r="W21" s="285"/>
-      <c r="X21" s="285"/>
-      <c r="Y21" s="285"/>
-      <c r="Z21" s="285"/>
-      <c r="AA21" s="285"/>
-      <c r="AB21" s="285"/>
-      <c r="AC21" s="285"/>
-      <c r="AD21" s="285"/>
-      <c r="AE21" s="285"/>
-      <c r="AF21" s="284"/>
+      <c r="V21" s="296"/>
+      <c r="W21" s="296"/>
+      <c r="X21" s="296"/>
+      <c r="Y21" s="296"/>
+      <c r="Z21" s="296"/>
+      <c r="AA21" s="296"/>
+      <c r="AB21" s="296"/>
+      <c r="AC21" s="296"/>
+      <c r="AD21" s="296"/>
+      <c r="AE21" s="296"/>
+      <c r="AF21" s="295"/>
     </row>
     <row r="22" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="142" t="s">
@@ -5969,7 +5965,7 @@
       <c r="U23" s="93" t="s">
         <v>301</v>
       </c>
-      <c r="V23" s="290" t="s">
+      <c r="V23" s="283" t="s">
         <v>356</v>
       </c>
       <c r="X23" s="139" t="s">
@@ -6801,10 +6797,10 @@
       </c>
     </row>
     <row r="34" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="283" t="s">
+      <c r="B34" s="294" t="s">
         <v>123</v>
       </c>
-      <c r="C34" s="284"/>
+      <c r="C34" s="295"/>
       <c r="E34" s="105" t="s">
         <v>62</v>
       </c>
@@ -7889,7 +7885,7 @@
         <v>266</v>
       </c>
       <c r="C46" s="249">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="E46" s="187" t="s">
         <v>351</v>
@@ -8264,11 +8260,11 @@
       <c r="C55" s="273">
         <v>0</v>
       </c>
-      <c r="U55" s="283" t="s">
+      <c r="U55" s="294" t="s">
         <v>332</v>
       </c>
-      <c r="V55" s="285"/>
-      <c r="W55" s="284"/>
+      <c r="V55" s="296"/>
+      <c r="W55" s="295"/>
       <c r="X55" s="93" t="s">
         <v>330</v>
       </c>
@@ -8569,23 +8565,23 @@
       </c>
     </row>
     <row r="3" spans="2:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="288" t="str">
+      <c r="B3" s="299" t="str">
         <f>CONCATENATE('QuickVal Proforma'!C5," | ","T12")</f>
         <v xml:space="preserve"> | T12</v>
       </c>
-      <c r="C3" s="288"/>
-      <c r="D3" s="288"/>
-      <c r="E3" s="288"/>
-      <c r="F3" s="288"/>
-      <c r="G3" s="288"/>
-      <c r="H3" s="288"/>
-      <c r="I3" s="288"/>
-      <c r="J3" s="288"/>
-      <c r="K3" s="288"/>
-      <c r="L3" s="288"/>
-      <c r="M3" s="288"/>
-      <c r="N3" s="288"/>
-      <c r="O3" s="288"/>
+      <c r="C3" s="299"/>
+      <c r="D3" s="299"/>
+      <c r="E3" s="299"/>
+      <c r="F3" s="299"/>
+      <c r="G3" s="299"/>
+      <c r="H3" s="299"/>
+      <c r="I3" s="299"/>
+      <c r="J3" s="299"/>
+      <c r="K3" s="299"/>
+      <c r="L3" s="299"/>
+      <c r="M3" s="299"/>
+      <c r="N3" s="299"/>
+      <c r="O3" s="299"/>
     </row>
     <row r="4" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="51" t="s">
@@ -12048,28 +12044,28 @@
     </row>
     <row r="2" spans="1:20" s="3" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="289" t="str">
+      <c r="B2" s="300" t="str">
         <f>CONCATENATE('QuickVal Proforma'!C5," | ","T12 Intake")</f>
         <v xml:space="preserve"> | T12 Intake</v>
       </c>
-      <c r="C2" s="289"/>
-      <c r="D2" s="289"/>
-      <c r="E2" s="289"/>
-      <c r="F2" s="289"/>
-      <c r="G2" s="289"/>
-      <c r="H2" s="289"/>
-      <c r="I2" s="289"/>
-      <c r="J2" s="289"/>
-      <c r="K2" s="289"/>
-      <c r="L2" s="289"/>
-      <c r="M2" s="289"/>
-      <c r="N2" s="289"/>
-      <c r="O2" s="289"/>
-      <c r="P2" s="289"/>
-      <c r="Q2" s="289"/>
-      <c r="R2" s="289"/>
-      <c r="S2" s="289"/>
-      <c r="T2" s="289"/>
+      <c r="C2" s="300"/>
+      <c r="D2" s="300"/>
+      <c r="E2" s="300"/>
+      <c r="F2" s="300"/>
+      <c r="G2" s="300"/>
+      <c r="H2" s="300"/>
+      <c r="I2" s="300"/>
+      <c r="J2" s="300"/>
+      <c r="K2" s="300"/>
+      <c r="L2" s="300"/>
+      <c r="M2" s="300"/>
+      <c r="N2" s="300"/>
+      <c r="O2" s="300"/>
+      <c r="P2" s="300"/>
+      <c r="Q2" s="300"/>
+      <c r="R2" s="300"/>
+      <c r="S2" s="300"/>
+      <c r="T2" s="300"/>
     </row>
     <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1"/>

--- a/templates/quickval_template.xlsx
+++ b/templates/quickval_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sammiller/Desktop/Mesirow/OMreader/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{794E917A-403A-7244-B950-D902F907E379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{66E17E31-75DD-D74F-A74B-6B57544418DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-37360" yWindow="500" windowWidth="37360" windowHeight="21100" activeTab="1" xr2:uid="{401FEA37-EBEB-4370-B91A-5CF478EDB23C}"/>
   </bookViews>
@@ -2453,7 +2453,6 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="22" fillId="9" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="17" fillId="2" borderId="25" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -2475,7 +2474,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="18" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="22" fillId="9" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="24" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2638,12 +2636,6 @@
     <xf numFmtId="5" fontId="29" fillId="9" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="29" fillId="9" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="22" fillId="9" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="22" fillId="9" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="22" fillId="9" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="22" fillId="9" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2764,6 +2756,14 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="22" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="22" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="22" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="22" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="22" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="29" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Comma" xfId="6" builtinId="3"/>
@@ -4165,591 +4165,591 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="182" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="184" t="s">
+      <c r="B1" s="182" t="s">
         <v>126</v>
       </c>
-      <c r="C1" s="184" t="s">
+      <c r="C1" s="182" t="s">
         <v>224</v>
       </c>
-      <c r="D1" s="184" t="s">
+      <c r="D1" s="182" t="s">
         <v>246</v>
       </c>
-      <c r="F1" s="184" t="s">
+      <c r="F1" s="182" t="s">
         <v>349</v>
       </c>
-      <c r="G1" s="234" t="s">
+      <c r="G1" s="232" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="221" t="s">
+      <c r="A2" s="219" t="s">
         <v>127</v>
       </c>
-      <c r="B2" s="221" t="s">
+      <c r="B2" s="219" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="221" t="s">
+      <c r="C2" s="219" t="s">
         <v>225</v>
       </c>
-      <c r="D2" s="221" t="s">
+      <c r="D2" s="219" t="s">
         <v>247</v>
       </c>
       <c r="F2" s="93" t="str">
         <f>CONCATENATE('QuickVal Proforma'!F4,'QuickVal Proforma'!G4)</f>
         <v>T12/T12 Actual</v>
       </c>
-      <c r="G2" s="235">
+      <c r="G2" s="233">
         <f>'QuickVal Proforma'!F5</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="221" t="s">
+      <c r="A3" s="219" t="s">
         <v>129</v>
       </c>
-      <c r="B3" s="221" t="s">
+      <c r="B3" s="219" t="s">
         <v>130</v>
       </c>
-      <c r="C3" s="221" t="s">
+      <c r="C3" s="219" t="s">
         <v>226</v>
       </c>
-      <c r="D3" s="221" t="s">
+      <c r="D3" s="219" t="s">
         <v>248</v>
       </c>
       <c r="F3" s="93" t="str">
         <f>'QuickVal Proforma'!I4</f>
         <v>&lt;--- RET &amp; OpEx adj.</v>
       </c>
-      <c r="G3" s="235" t="e">
+      <c r="G3" s="233" t="e">
         <f>'QuickVal Proforma'!I5</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="221" t="s">
+      <c r="A4" s="219" t="s">
         <v>131</v>
       </c>
-      <c r="B4" s="221" t="s">
+      <c r="B4" s="219" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="221" t="s">
+      <c r="C4" s="219" t="s">
         <v>227</v>
       </c>
-      <c r="D4" s="221" t="s">
+      <c r="D4" s="219" t="s">
         <v>249</v>
       </c>
       <c r="F4" s="93" t="str">
         <f>'QuickVal Proforma'!L4</f>
         <v>&lt;--- w/ Revenue Losses stblz.</v>
       </c>
-      <c r="G4" s="235" t="e">
+      <c r="G4" s="233" t="e">
         <f>'QuickVal Proforma'!L5</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="221" t="s">
+      <c r="A5" s="219" t="s">
         <v>133</v>
       </c>
-      <c r="B5" s="221" t="s">
+      <c r="B5" s="219" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="221" t="s">
+      <c r="C5" s="219" t="s">
         <v>228</v>
       </c>
-      <c r="D5" s="221" t="s">
+      <c r="D5" s="219" t="s">
         <v>250</v>
       </c>
       <c r="F5" s="93" t="str">
         <f>'QuickVal Proforma'!O4</f>
         <v>Untrended Stablized</v>
       </c>
-      <c r="G5" s="235" t="e">
+      <c r="G5" s="233" t="e">
         <f>'QuickVal Proforma'!O5</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="221" t="s">
+      <c r="A6" s="219" t="s">
         <v>134</v>
       </c>
-      <c r="B6" s="221" t="s">
+      <c r="B6" s="219" t="s">
         <v>135</v>
       </c>
-      <c r="C6" s="221" t="s">
+      <c r="C6" s="219" t="s">
         <v>229</v>
       </c>
-      <c r="D6" s="221" t="s">
+      <c r="D6" s="219" t="s">
         <v>251</v>
       </c>
       <c r="F6" s="93" t="str">
         <f>'QuickVal Proforma'!B29</f>
         <v>Exit Cap Rate</v>
       </c>
-      <c r="G6" s="235">
+      <c r="G6" s="233">
         <f>'QuickVal Proforma'!C29</f>
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="221" t="s">
+      <c r="A7" s="219" t="s">
         <v>136</v>
       </c>
-      <c r="B7" s="221" t="s">
+      <c r="B7" s="219" t="s">
         <v>137</v>
       </c>
-      <c r="C7" s="221" t="s">
+      <c r="C7" s="219" t="s">
         <v>230</v>
       </c>
-      <c r="D7" s="221" t="s">
+      <c r="D7" s="219" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="221" t="s">
+      <c r="A8" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="B8" s="221" t="s">
+      <c r="B8" s="219" t="s">
         <v>139</v>
       </c>
-      <c r="C8" s="221" t="s">
+      <c r="C8" s="219" t="s">
         <v>231</v>
       </c>
-      <c r="D8" s="221" t="s">
+      <c r="D8" s="219" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="221" t="s">
+      <c r="A9" s="219" t="s">
         <v>135</v>
       </c>
-      <c r="B9" s="221" t="s">
+      <c r="B9" s="219" t="s">
         <v>140</v>
       </c>
-      <c r="C9" s="221" t="s">
+      <c r="C9" s="219" t="s">
         <v>232</v>
       </c>
-      <c r="D9" s="221" t="s">
+      <c r="D9" s="219" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="221" t="s">
+      <c r="A10" s="219" t="s">
         <v>141</v>
       </c>
-      <c r="B10" s="221" t="s">
+      <c r="B10" s="219" t="s">
         <v>142</v>
       </c>
-      <c r="C10" s="221" t="s">
+      <c r="C10" s="219" t="s">
         <v>233</v>
       </c>
-      <c r="D10" s="221" t="s">
+      <c r="D10" s="219" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="221" t="s">
+      <c r="A11" s="219" t="s">
         <v>143</v>
       </c>
-      <c r="B11" s="221" t="s">
+      <c r="B11" s="219" t="s">
         <v>144</v>
       </c>
-      <c r="C11" s="221" t="s">
+      <c r="C11" s="219" t="s">
         <v>234</v>
       </c>
-      <c r="D11" s="221" t="s">
+      <c r="D11" s="219" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="221" t="s">
+      <c r="A12" s="219" t="s">
         <v>145</v>
       </c>
-      <c r="B12" s="221" t="s">
+      <c r="B12" s="219" t="s">
         <v>146</v>
       </c>
-      <c r="C12" s="221" t="s">
+      <c r="C12" s="219" t="s">
         <v>235</v>
       </c>
-      <c r="D12" s="221" t="s">
+      <c r="D12" s="219" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="221" t="s">
+      <c r="A13" s="219" t="s">
         <v>147</v>
       </c>
-      <c r="B13" s="221" t="s">
+      <c r="B13" s="219" t="s">
         <v>148</v>
       </c>
-      <c r="C13" s="221" t="s">
+      <c r="C13" s="219" t="s">
         <v>236</v>
       </c>
-      <c r="D13" s="221" t="s">
+      <c r="D13" s="219" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="221" t="s">
+      <c r="A14" s="219" t="s">
         <v>149</v>
       </c>
-      <c r="B14" s="221" t="s">
+      <c r="B14" s="219" t="s">
         <v>150</v>
       </c>
-      <c r="C14" s="221" t="s">
+      <c r="C14" s="219" t="s">
         <v>237</v>
       </c>
-      <c r="D14" s="221" t="s">
+      <c r="D14" s="219" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="221" t="s">
+      <c r="A15" s="219" t="s">
         <v>151</v>
       </c>
-      <c r="B15" s="221" t="s">
+      <c r="B15" s="219" t="s">
         <v>152</v>
       </c>
-      <c r="C15" s="221" t="s">
+      <c r="C15" s="219" t="s">
         <v>238</v>
       </c>
-      <c r="D15" s="221" t="s">
+      <c r="D15" s="219" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="221" t="s">
+      <c r="A16" s="219" t="s">
         <v>153</v>
       </c>
-      <c r="B16" s="221" t="s">
+      <c r="B16" s="219" t="s">
         <v>147</v>
       </c>
-      <c r="C16" s="221" t="s">
+      <c r="C16" s="219" t="s">
         <v>239</v>
       </c>
-      <c r="D16" s="221" t="s">
+      <c r="D16" s="219" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="221" t="s">
+      <c r="A17" s="219" t="s">
         <v>154</v>
       </c>
-      <c r="B17" s="221" t="s">
+      <c r="B17" s="219" t="s">
         <v>155</v>
       </c>
-      <c r="C17" s="221" t="s">
+      <c r="C17" s="219" t="s">
         <v>240</v>
       </c>
-      <c r="D17" s="221" t="s">
+      <c r="D17" s="219" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="221" t="s">
+      <c r="A18" s="219" t="s">
         <v>156</v>
       </c>
-      <c r="B18" s="221" t="s">
+      <c r="B18" s="219" t="s">
         <v>157</v>
       </c>
-      <c r="C18" s="221" t="s">
+      <c r="C18" s="219" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="221" t="s">
+      <c r="A19" s="219" t="s">
         <v>158</v>
       </c>
-      <c r="B19" s="221" t="s">
+      <c r="B19" s="219" t="s">
         <v>159</v>
       </c>
-      <c r="C19" s="221" t="s">
+      <c r="C19" s="219" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="221" t="s">
+      <c r="A20" s="219" t="s">
         <v>160</v>
       </c>
-      <c r="B20" s="221" t="s">
+      <c r="B20" s="219" t="s">
         <v>161</v>
       </c>
-      <c r="C20" s="221" t="s">
+      <c r="C20" s="219" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="221" t="s">
+      <c r="A21" s="219" t="s">
         <v>162</v>
       </c>
-      <c r="B21" s="221" t="s">
+      <c r="B21" s="219" t="s">
         <v>163</v>
       </c>
-      <c r="C21" s="221" t="s">
+      <c r="C21" s="219" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="221" t="s">
+      <c r="A22" s="219" t="s">
         <v>164</v>
       </c>
-      <c r="B22" s="221" t="s">
+      <c r="B22" s="219" t="s">
         <v>165</v>
       </c>
-      <c r="C22" s="221" t="s">
+      <c r="C22" s="219" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="221" t="s">
+      <c r="A23" s="219" t="s">
         <v>166</v>
       </c>
-      <c r="B23" s="221" t="s">
+      <c r="B23" s="219" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="221" t="s">
+      <c r="A24" s="219" t="s">
         <v>168</v>
       </c>
-      <c r="B24" s="221" t="s">
+      <c r="B24" s="219" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="221" t="s">
+      <c r="A25" s="219" t="s">
         <v>170</v>
       </c>
-      <c r="B25" s="221" t="s">
+      <c r="B25" s="219" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="221" t="s">
+      <c r="A26" s="219" t="s">
         <v>172</v>
       </c>
-      <c r="B26" s="221" t="s">
+      <c r="B26" s="219" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="221" t="s">
+      <c r="A27" s="219" t="s">
         <v>174</v>
       </c>
-      <c r="B27" s="221" t="s">
+      <c r="B27" s="219" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="221" t="s">
+      <c r="A28" s="219" t="s">
         <v>176</v>
       </c>
-      <c r="B28" s="221" t="s">
+      <c r="B28" s="219" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="221" t="s">
+      <c r="A29" s="219" t="s">
         <v>178</v>
       </c>
-      <c r="B29" s="221" t="s">
+      <c r="B29" s="219" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="221" t="s">
+      <c r="A30" s="219" t="s">
         <v>180</v>
       </c>
-      <c r="B30" s="221" t="s">
+      <c r="B30" s="219" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="221" t="s">
+      <c r="A31" s="219" t="s">
         <v>182</v>
       </c>
-      <c r="B31" s="221" t="s">
+      <c r="B31" s="219" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="221" t="s">
+      <c r="A32" s="219" t="s">
         <v>184</v>
       </c>
-      <c r="B32" s="221" t="s">
+      <c r="B32" s="219" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="221" t="s">
+      <c r="A33" s="219" t="s">
         <v>186</v>
       </c>
-      <c r="B33" s="221" t="s">
+      <c r="B33" s="219" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="221" t="s">
+      <c r="A34" s="219" t="s">
         <v>188</v>
       </c>
-      <c r="B34" s="221" t="s">
+      <c r="B34" s="219" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="221" t="s">
+      <c r="A35" s="219" t="s">
         <v>190</v>
       </c>
-      <c r="B35" s="221" t="s">
+      <c r="B35" s="219" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="221" t="s">
+      <c r="A36" s="219" t="s">
         <v>192</v>
       </c>
-      <c r="B36" s="221" t="s">
+      <c r="B36" s="219" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="221" t="s">
+      <c r="A37" s="219" t="s">
         <v>194</v>
       </c>
-      <c r="B37" s="221" t="s">
+      <c r="B37" s="219" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="221" t="s">
+      <c r="A38" s="219" t="s">
         <v>196</v>
       </c>
-      <c r="B38" s="221" t="s">
+      <c r="B38" s="219" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="221" t="s">
+      <c r="A39" s="219" t="s">
         <v>198</v>
       </c>
-      <c r="B39" s="221" t="s">
+      <c r="B39" s="219" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="221" t="s">
+      <c r="A40" s="219" t="s">
         <v>200</v>
       </c>
-      <c r="B40" s="221" t="s">
+      <c r="B40" s="219" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="221" t="s">
+      <c r="A41" s="219" t="s">
         <v>202</v>
       </c>
-      <c r="B41" s="221" t="s">
+      <c r="B41" s="219" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="221" t="s">
+      <c r="A42" s="219" t="s">
         <v>204</v>
       </c>
-      <c r="B42" s="221" t="s">
+      <c r="B42" s="219" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" s="221" t="s">
+      <c r="A43" s="219" t="s">
         <v>206</v>
       </c>
-      <c r="B43" s="221" t="s">
+      <c r="B43" s="219" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" s="221" t="s">
+      <c r="A44" s="219" t="s">
         <v>207</v>
       </c>
-      <c r="B44" s="221" t="s">
+      <c r="B44" s="219" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" s="221" t="s">
+      <c r="A45" s="219" t="s">
         <v>209</v>
       </c>
-      <c r="B45" s="221" t="s">
+      <c r="B45" s="219" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" s="221" t="s">
+      <c r="A46" s="219" t="s">
         <v>211</v>
       </c>
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="219" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" s="221" t="s">
+      <c r="A47" s="219" t="s">
         <v>212</v>
       </c>
-      <c r="B47" s="221" t="s">
+      <c r="B47" s="219" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" s="221" t="s">
+      <c r="A48" s="219" t="s">
         <v>214</v>
       </c>
-      <c r="B48" s="221" t="s">
+      <c r="B48" s="219" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" s="221" t="s">
+      <c r="A49" s="219" t="s">
         <v>216</v>
       </c>
-      <c r="B49" s="221" t="s">
+      <c r="B49" s="219" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" s="221" t="s">
+      <c r="A50" s="219" t="s">
         <v>218</v>
       </c>
-      <c r="B50" s="221" t="s">
+      <c r="B50" s="219" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51" s="221" t="s">
+      <c r="A51" s="219" t="s">
         <v>220</v>
       </c>
-      <c r="B51" s="221" t="s">
+      <c r="B51" s="219" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52" s="221" t="s">
+      <c r="A52" s="219" t="s">
         <v>222</v>
       </c>
-      <c r="B52" s="221" t="s">
+      <c r="B52" s="219" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B53" s="221" t="s">
+      <c r="B53" s="219" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B54" s="221" t="s">
+      <c r="B54" s="219" t="s">
         <v>223</v>
       </c>
     </row>
@@ -4788,65 +4788,65 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="297" t="str">
+      <c r="B2" s="291" t="str">
         <f>CONCATENATE(C5," | ","Quick Valuation")</f>
         <v xml:space="preserve"> | Quick Valuation</v>
       </c>
-      <c r="C2" s="297"/>
-      <c r="D2" s="297"/>
-      <c r="E2" s="297"/>
-      <c r="F2" s="297"/>
-      <c r="G2" s="297"/>
-      <c r="H2" s="297"/>
-      <c r="I2" s="297"/>
-      <c r="J2" s="297"/>
-      <c r="K2" s="297"/>
-      <c r="L2" s="297"/>
-      <c r="M2" s="297"/>
-      <c r="N2" s="297"/>
-      <c r="O2" s="297"/>
-      <c r="P2" s="297"/>
-      <c r="Q2" s="297"/>
-      <c r="R2" s="297"/>
-      <c r="S2" s="297"/>
+      <c r="C2" s="291"/>
+      <c r="D2" s="291"/>
+      <c r="E2" s="291"/>
+      <c r="F2" s="291"/>
+      <c r="G2" s="291"/>
+      <c r="H2" s="291"/>
+      <c r="I2" s="291"/>
+      <c r="J2" s="291"/>
+      <c r="K2" s="291"/>
+      <c r="L2" s="291"/>
+      <c r="M2" s="291"/>
+      <c r="N2" s="291"/>
+      <c r="O2" s="291"/>
+      <c r="P2" s="291"/>
+      <c r="Q2" s="291"/>
+      <c r="R2" s="291"/>
+      <c r="S2" s="291"/>
     </row>
     <row r="3" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="280">
+      <c r="B3" s="274">
         <f ca="1">TODAY()</f>
         <v>46136</v>
       </c>
-      <c r="R3" s="298">
+      <c r="R3" s="292">
         <v>5</v>
       </c>
-      <c r="S3" s="298"/>
+      <c r="S3" s="292"/>
     </row>
     <row r="4" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="294" t="s">
+      <c r="B4" s="288" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="295"/>
-      <c r="F4" s="284" t="s">
+      <c r="C4" s="289"/>
+      <c r="F4" s="278" t="s">
         <v>93</v>
       </c>
       <c r="G4" s="94" t="s">
         <v>115</v>
       </c>
-      <c r="I4" s="228" t="s">
+      <c r="I4" s="226" t="s">
         <v>116</v>
       </c>
-      <c r="J4" s="229"/>
-      <c r="L4" s="228" t="s">
+      <c r="J4" s="227"/>
+      <c r="L4" s="226" t="s">
         <v>345</v>
       </c>
-      <c r="M4" s="229"/>
-      <c r="O4" s="230" t="s">
+      <c r="M4" s="227"/>
+      <c r="O4" s="228" t="s">
         <v>88</v>
       </c>
-      <c r="P4" s="231"/>
-      <c r="R4" s="230" t="s">
+      <c r="P4" s="229"/>
+      <c r="R4" s="228" t="s">
         <v>336</v>
       </c>
-      <c r="S4" s="231"/>
+      <c r="S4" s="229"/>
       <c r="U4" s="95" t="s">
         <v>286</v>
       </c>
@@ -4864,39 +4864,39 @@
       <c r="B5" s="98" t="s">
         <v>75</v>
       </c>
-      <c r="C5" s="237"/>
-      <c r="F5" s="232">
+      <c r="C5" s="235"/>
+      <c r="F5" s="230">
         <f>F48/$C$23</f>
         <v>0</v>
       </c>
-      <c r="G5" s="233"/>
-      <c r="I5" s="232" t="e">
+      <c r="G5" s="231"/>
+      <c r="I5" s="230" t="e">
         <f>I48/$C$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J5" s="233"/>
-      <c r="L5" s="232" t="e">
+      <c r="J5" s="231"/>
+      <c r="L5" s="230" t="e">
         <f>L48/$C$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M5" s="233"/>
-      <c r="O5" s="232" t="e">
+      <c r="M5" s="231"/>
+      <c r="O5" s="230" t="e">
         <f>O48/($C$27)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P5" s="233"/>
-      <c r="R5" s="232" t="e">
+      <c r="P5" s="231"/>
+      <c r="R5" s="230" t="e">
         <f>R48/$C$27</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S5" s="233"/>
+      <c r="S5" s="231"/>
       <c r="U5" s="99" t="s">
         <v>271</v>
       </c>
-      <c r="V5" s="285">
+      <c r="V5" s="279">
         <v>95000</v>
       </c>
-      <c r="W5" s="286">
+      <c r="W5" s="280">
         <v>0</v>
       </c>
       <c r="X5" s="100">
@@ -4908,7 +4908,7 @@
       <c r="B6" s="98" t="s">
         <v>262</v>
       </c>
-      <c r="C6" s="238"/>
+      <c r="C6" s="236"/>
       <c r="E6" s="101" t="s">
         <v>76</v>
       </c>
@@ -4946,10 +4946,10 @@
       <c r="U6" s="99" t="s">
         <v>272</v>
       </c>
-      <c r="V6" s="285">
+      <c r="V6" s="279">
         <v>65000</v>
       </c>
-      <c r="W6" s="286">
+      <c r="W6" s="280">
         <v>0</v>
       </c>
       <c r="X6" s="100">
@@ -4961,7 +4961,7 @@
       <c r="B7" s="98" t="s">
         <v>98</v>
       </c>
-      <c r="C7" s="238"/>
+      <c r="C7" s="236"/>
       <c r="E7" s="105" t="s">
         <v>42</v>
       </c>
@@ -5008,10 +5008,10 @@
       <c r="U7" s="99" t="s">
         <v>273</v>
       </c>
-      <c r="V7" s="285">
+      <c r="V7" s="279">
         <v>55000</v>
       </c>
-      <c r="W7" s="286">
+      <c r="W7" s="280">
         <v>0</v>
       </c>
       <c r="X7" s="100">
@@ -5023,7 +5023,7 @@
       <c r="B8" s="98" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="237"/>
+      <c r="C8" s="235"/>
       <c r="E8" s="105" t="s">
         <v>43</v>
       </c>
@@ -5070,10 +5070,10 @@
       <c r="U8" s="99" t="s">
         <v>274</v>
       </c>
-      <c r="V8" s="285">
+      <c r="V8" s="279">
         <v>50000</v>
       </c>
-      <c r="W8" s="286">
+      <c r="W8" s="280">
         <v>0</v>
       </c>
       <c r="X8" s="100">
@@ -5085,7 +5085,7 @@
       <c r="B9" s="98" t="s">
         <v>100</v>
       </c>
-      <c r="C9" s="237"/>
+      <c r="C9" s="235"/>
       <c r="E9" s="105" t="s">
         <v>44</v>
       </c>
@@ -5117,7 +5117,7 @@
         <f>O7*-P9</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P9" s="266">
+      <c r="P9" s="260">
         <f>IF($C$36&gt;2%,$C$36/2,1%)</f>
         <v>0.01</v>
       </c>
@@ -5132,10 +5132,10 @@
       <c r="U9" s="110" t="s">
         <v>275</v>
       </c>
-      <c r="V9" s="287">
+      <c r="V9" s="281">
         <v>50000</v>
       </c>
-      <c r="W9" s="288">
+      <c r="W9" s="282">
         <v>0</v>
       </c>
       <c r="X9" s="111">
@@ -5147,7 +5147,7 @@
       <c r="B10" s="112" t="s">
         <v>263</v>
       </c>
-      <c r="C10" s="236">
+      <c r="C10" s="234">
         <f ca="1">TODAY()+30</f>
         <v>46166</v>
       </c>
@@ -5197,10 +5197,10 @@
       <c r="U10" s="99" t="s">
         <v>276</v>
       </c>
-      <c r="V10" s="285">
+      <c r="V10" s="279">
         <v>75000</v>
       </c>
-      <c r="W10" s="286">
+      <c r="W10" s="280">
         <v>0</v>
       </c>
       <c r="X10" s="100">
@@ -5212,7 +5212,7 @@
       <c r="B11" s="98" t="s">
         <v>101</v>
       </c>
-      <c r="C11" s="237"/>
+      <c r="C11" s="235"/>
       <c r="E11" s="105" t="s">
         <v>45</v>
       </c>
@@ -5236,7 +5236,7 @@
         <f>SUM($L$7:$L$8)*-M11</f>
         <v>0</v>
       </c>
-      <c r="M11" s="267">
+      <c r="M11" s="261">
         <v>0.05</v>
       </c>
       <c r="O11" s="106" t="e">
@@ -5258,10 +5258,10 @@
       <c r="U11" s="99" t="s">
         <v>277</v>
       </c>
-      <c r="V11" s="285">
+      <c r="V11" s="279">
         <v>55000</v>
       </c>
-      <c r="W11" s="286">
+      <c r="W11" s="280">
         <v>0</v>
       </c>
       <c r="X11" s="100">
@@ -5273,7 +5273,7 @@
       <c r="B12" s="98" t="s">
         <v>105</v>
       </c>
-      <c r="C12" s="239"/>
+      <c r="C12" s="237"/>
       <c r="E12" s="105" t="s">
         <v>46</v>
       </c>
@@ -5297,7 +5297,7 @@
         <f>$L$7*-M12</f>
         <v>0</v>
       </c>
-      <c r="M12" s="267">
+      <c r="M12" s="261">
         <v>1E-3</v>
       </c>
       <c r="O12" s="106" t="e">
@@ -5319,10 +5319,10 @@
       <c r="U12" s="99" t="s">
         <v>278</v>
       </c>
-      <c r="V12" s="285">
+      <c r="V12" s="279">
         <v>45000</v>
       </c>
-      <c r="W12" s="286">
+      <c r="W12" s="280">
         <v>0</v>
       </c>
       <c r="X12" s="100">
@@ -5334,7 +5334,7 @@
       <c r="B13" s="98" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="239" t="e">
+      <c r="C13" s="237" t="e">
         <f>259008/Units</f>
         <v>#DIV/0!</v>
       </c>
@@ -5361,7 +5361,7 @@
         <f>$L$7/Units*-M13</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M13" s="268">
+      <c r="M13" s="262">
         <v>1.25</v>
       </c>
       <c r="O13" s="106" t="e">
@@ -5383,10 +5383,10 @@
       <c r="U13" s="99" t="s">
         <v>279</v>
       </c>
-      <c r="V13" s="285">
+      <c r="V13" s="279">
         <v>35000</v>
       </c>
-      <c r="W13" s="286">
+      <c r="W13" s="280">
         <v>0</v>
       </c>
       <c r="X13" s="100">
@@ -5398,7 +5398,7 @@
       <c r="B14" s="112" t="s">
         <v>268</v>
       </c>
-      <c r="C14" s="240"/>
+      <c r="C14" s="238"/>
       <c r="E14" s="117" t="s">
         <v>48</v>
       </c>
@@ -5422,7 +5422,7 @@
         <f>$L$7/Units*-M14</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M14" s="268">
+      <c r="M14" s="262">
         <v>0</v>
       </c>
       <c r="O14" s="106" t="e">
@@ -5444,10 +5444,10 @@
       <c r="U14" s="119" t="s">
         <v>280</v>
       </c>
-      <c r="V14" s="289">
+      <c r="V14" s="283">
         <v>50000</v>
       </c>
-      <c r="W14" s="290">
+      <c r="W14" s="284">
         <v>0</v>
       </c>
       <c r="X14" s="120">
@@ -5459,7 +5459,7 @@
       <c r="B15" s="98" t="s">
         <v>104</v>
       </c>
-      <c r="C15" s="237"/>
+      <c r="C15" s="235"/>
       <c r="E15" s="117" t="s">
         <v>49</v>
       </c>
@@ -5483,7 +5483,7 @@
         <f>$L$7*-M15</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M15" s="267" t="e">
+      <c r="M15" s="261" t="e">
         <f>1/Units</f>
         <v>#DIV/0!</v>
       </c>
@@ -5506,7 +5506,7 @@
       <c r="U15" s="121" t="s">
         <v>281</v>
       </c>
-      <c r="W15" s="291">
+      <c r="W15" s="285">
         <f>SUM(W5:W14)</f>
         <v>0</v>
       </c>
@@ -5519,7 +5519,7 @@
       <c r="B16" s="98" t="s">
         <v>103</v>
       </c>
-      <c r="C16" s="237"/>
+      <c r="C16" s="235"/>
       <c r="E16" s="113" t="s">
         <v>78</v>
       </c>
@@ -5566,7 +5566,7 @@
       <c r="U16" s="99" t="s">
         <v>288</v>
       </c>
-      <c r="W16" s="292">
+      <c r="W16" s="286">
         <v>0.12</v>
       </c>
       <c r="X16" s="100">
@@ -5578,7 +5578,7 @@
       <c r="B17" s="98" t="s">
         <v>106</v>
       </c>
-      <c r="C17" s="238"/>
+      <c r="C17" s="236"/>
       <c r="E17" s="123" t="s">
         <v>79</v>
       </c>
@@ -5596,7 +5596,7 @@
         <v>282</v>
       </c>
       <c r="V17" s="127"/>
-      <c r="W17" s="293">
+      <c r="W17" s="287">
         <v>0.28000000000000003</v>
       </c>
       <c r="X17" s="120">
@@ -5608,7 +5608,7 @@
       <c r="B18" s="133" t="s">
         <v>114</v>
       </c>
-      <c r="C18" s="257"/>
+      <c r="C18" s="251"/>
       <c r="E18" s="105" t="s">
         <v>50</v>
       </c>
@@ -5696,7 +5696,7 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O19" s="270">
+      <c r="O19" s="264">
         <f>L19</f>
         <v>0</v>
       </c>
@@ -5728,10 +5728,10 @@
       </c>
     </row>
     <row r="20" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="294" t="s">
+      <c r="B20" s="288" t="s">
         <v>107</v>
       </c>
-      <c r="C20" s="295"/>
+      <c r="C20" s="289"/>
       <c r="E20" s="105" t="s">
         <v>52</v>
       </c>
@@ -5759,7 +5759,7 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O20" s="270">
+      <c r="O20" s="264">
         <f t="shared" ref="O20:O22" si="14">L20</f>
         <v>0</v>
       </c>
@@ -5780,7 +5780,7 @@
       <c r="B21" s="98" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="241"/>
+      <c r="C21" s="239"/>
       <c r="E21" s="105" t="s">
         <v>53</v>
       </c>
@@ -5808,7 +5808,7 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O21" s="270">
+      <c r="O21" s="264">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -5824,20 +5824,20 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U21" s="294" t="s">
+      <c r="U21" s="288" t="s">
         <v>300</v>
       </c>
-      <c r="V21" s="296"/>
-      <c r="W21" s="296"/>
-      <c r="X21" s="296"/>
-      <c r="Y21" s="296"/>
-      <c r="Z21" s="296"/>
-      <c r="AA21" s="296"/>
-      <c r="AB21" s="296"/>
-      <c r="AC21" s="296"/>
-      <c r="AD21" s="296"/>
-      <c r="AE21" s="296"/>
-      <c r="AF21" s="295"/>
+      <c r="V21" s="290"/>
+      <c r="W21" s="290"/>
+      <c r="X21" s="290"/>
+      <c r="Y21" s="290"/>
+      <c r="Z21" s="290"/>
+      <c r="AA21" s="290"/>
+      <c r="AB21" s="290"/>
+      <c r="AC21" s="290"/>
+      <c r="AD21" s="290"/>
+      <c r="AE21" s="290"/>
+      <c r="AF21" s="289"/>
     </row>
     <row r="22" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="142" t="s">
@@ -5874,7 +5874,7 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O22" s="270">
+      <c r="O22" s="264">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -5893,7 +5893,7 @@
       <c r="U22" s="93" t="s">
         <v>301</v>
       </c>
-      <c r="V22" s="250">
+      <c r="V22" s="244">
         <v>2026</v>
       </c>
       <c r="X22" s="139" t="s">
@@ -5916,7 +5916,7 @@
         <f>IF(C21&gt;0,CONCATENATE("Purchase Price (",ROUND(C23/C21*100,1),"% whisp.)"),"Purchase Price")</f>
         <v>Purchase Price</v>
       </c>
-      <c r="C23" s="242">
+      <c r="C23" s="240">
         <v>100000000</v>
       </c>
       <c r="E23" s="105" t="s">
@@ -5950,7 +5950,7 @@
         <f>P23*O37</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P23" s="269" t="e">
+      <c r="P23" s="263" t="e">
         <f>G23</f>
         <v>#DIV/0!</v>
       </c>
@@ -5965,13 +5965,13 @@
       <c r="U23" s="93" t="s">
         <v>301</v>
       </c>
-      <c r="V23" s="283" t="s">
+      <c r="V23" s="277" t="s">
         <v>356</v>
       </c>
       <c r="X23" s="139" t="s">
         <v>323</v>
       </c>
-      <c r="Y23" s="250">
+      <c r="Y23" s="244">
         <v>1</v>
       </c>
       <c r="AA23" s="141" t="s">
@@ -6043,7 +6043,7 @@
       <c r="X24" s="139" t="s">
         <v>324</v>
       </c>
-      <c r="Y24" s="251">
+      <c r="Y24" s="245">
         <v>0.02</v>
       </c>
     </row>
@@ -6051,7 +6051,7 @@
       <c r="B25" s="98" t="s">
         <v>341</v>
       </c>
-      <c r="C25" s="244">
+      <c r="C25" s="299">
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="E25" s="105" t="s">
@@ -6116,8 +6116,8 @@
       <c r="B26" s="98" t="s">
         <v>348</v>
       </c>
-      <c r="C26" s="244">
-        <v>6.0000000000000001E-3</v>
+      <c r="C26" s="299">
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="E26" s="148" t="s">
         <v>81</v>
@@ -6168,7 +6168,7 @@
       <c r="B27" s="98" t="s">
         <v>342</v>
       </c>
-      <c r="C27" s="211">
+      <c r="C27" s="209">
         <f>IFERROR(C23+(C23*C25)+(C23*C26)+W60,0)</f>
         <v>0</v>
       </c>
@@ -6241,94 +6241,94 @@
       <c r="E28" s="123" t="s">
         <v>82</v>
       </c>
-      <c r="F28" s="157" t="str">
+      <c r="F28" s="156" t="str">
         <f>F6</f>
         <v>Jul-25 T12</v>
       </c>
-      <c r="G28" s="158" t="str">
+      <c r="G28" s="157" t="str">
         <f>G6</f>
         <v>Per Unit</v>
       </c>
-      <c r="I28" s="157" t="str">
+      <c r="I28" s="156" t="str">
         <f>I6</f>
         <v>RET &amp; OpEx adj.</v>
       </c>
-      <c r="J28" s="158" t="str">
+      <c r="J28" s="157" t="str">
         <f>J6</f>
         <v>Per Unit</v>
       </c>
-      <c r="L28" s="157" t="str">
+      <c r="L28" s="156" t="str">
         <f>L6</f>
         <v>Stabilized Losses</v>
       </c>
-      <c r="M28" s="159" t="str">
+      <c r="M28" s="158" t="str">
         <f>M6</f>
         <v>Per Unit</v>
       </c>
-      <c r="O28" s="157" t="str">
+      <c r="O28" s="156" t="str">
         <f>O6</f>
         <v>Untrended</v>
       </c>
-      <c r="P28" s="158"/>
-      <c r="R28" s="157" t="str">
+      <c r="P28" s="157"/>
+      <c r="R28" s="156" t="str">
         <f>R6</f>
         <v>Trended</v>
       </c>
-      <c r="S28" s="158"/>
+      <c r="S28" s="157"/>
       <c r="U28" s="93" t="s">
         <v>304</v>
       </c>
-      <c r="W28" s="251">
+      <c r="W28" s="245">
         <v>0.02</v>
       </c>
-      <c r="X28" s="160">
+      <c r="X28" s="159">
         <f>W28</f>
         <v>0.02</v>
       </c>
-      <c r="Y28" s="160">
+      <c r="Y28" s="159">
         <f t="shared" ref="Y28:AA28" si="19">X28</f>
         <v>0.02</v>
       </c>
-      <c r="Z28" s="160">
+      <c r="Z28" s="159">
         <f t="shared" si="19"/>
         <v>0.02</v>
       </c>
-      <c r="AA28" s="160">
+      <c r="AA28" s="159">
         <f t="shared" si="19"/>
         <v>0.02</v>
       </c>
-      <c r="AB28" s="160">
+      <c r="AB28" s="159">
         <f t="shared" ref="AB28:AF28" si="20">AA28</f>
         <v>0.02</v>
       </c>
-      <c r="AC28" s="160">
+      <c r="AC28" s="159">
         <f t="shared" si="20"/>
         <v>0.02</v>
       </c>
-      <c r="AD28" s="160">
+      <c r="AD28" s="159">
         <f t="shared" si="20"/>
         <v>0.02</v>
       </c>
-      <c r="AE28" s="160">
+      <c r="AE28" s="159">
         <f t="shared" si="20"/>
         <v>0.02</v>
       </c>
-      <c r="AF28" s="160">
+      <c r="AF28" s="159">
         <f t="shared" si="20"/>
         <v>0.02</v>
       </c>
     </row>
     <row r="29" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="217" t="s">
+      <c r="B29" s="215" t="s">
         <v>337</v>
       </c>
-      <c r="C29" s="243">
+      <c r="C29" s="300">
         <v>5.2499999999999998E-2</v>
       </c>
       <c r="E29" s="105" t="s">
         <v>57</v>
       </c>
-      <c r="F29" s="161">
+      <c r="F29" s="160">
         <f>IFERROR('T12 Clean'!O27,0)</f>
         <v>0</v>
       </c>
@@ -6336,15 +6336,15 @@
         <f t="shared" ref="G29:G34" si="21">IFERROR(F29/Units,0)</f>
         <v>0</v>
       </c>
-      <c r="I29" s="161">
+      <c r="I29" s="160">
         <f t="shared" ref="I29:I34" si="22">J29*Units</f>
         <v>0</v>
       </c>
-      <c r="J29" s="265">
+      <c r="J29" s="259">
         <f>G29*(1+$C$40)</f>
         <v>0</v>
       </c>
-      <c r="L29" s="162">
+      <c r="L29" s="161">
         <f>I29</f>
         <v>0</v>
       </c>
@@ -6352,7 +6352,7 @@
         <f t="shared" ref="M29:M35" si="23">L29/Units</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O29" s="162">
+      <c r="O29" s="161">
         <f>L29</f>
         <v>0</v>
       </c>
@@ -6360,7 +6360,7 @@
         <f t="shared" ref="P29:P35" si="24">O29/Units</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R29" s="162">
+      <c r="R29" s="161">
         <f t="shared" ref="R29:R34" si="25">O29*(1+$C$40)^($R$3-1)</f>
         <v>0</v>
       </c>
@@ -6371,10 +6371,10 @@
       <c r="U29" s="93" t="s">
         <v>305</v>
       </c>
-      <c r="V29" s="252">
+      <c r="V29" s="246">
         <v>90000000</v>
       </c>
-      <c r="W29" s="252">
+      <c r="W29" s="246">
         <v>90000000</v>
       </c>
       <c r="X29" s="140">
@@ -6418,7 +6418,7 @@
       <c r="B30" s="98" t="s">
         <v>338</v>
       </c>
-      <c r="C30" s="211">
+      <c r="C30" s="209">
         <f>IFERROR((R46-(J47*(1+$C$40)^(R3-1))*Units)/C29,0)</f>
         <v>0</v>
       </c>
@@ -6437,7 +6437,7 @@
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J30" s="265">
+      <c r="J30" s="259">
         <f t="shared" ref="J30:J33" si="28">G30*(1+$C$40)</f>
         <v>0</v>
       </c>
@@ -6468,41 +6468,41 @@
       <c r="U30" s="93" t="s">
         <v>306</v>
       </c>
-      <c r="W30" s="218">
+      <c r="W30" s="216">
         <v>1</v>
       </c>
-      <c r="X30" s="258">
+      <c r="X30" s="252">
         <v>1</v>
       </c>
-      <c r="Y30" s="219">
+      <c r="Y30" s="217">
         <f t="shared" ref="Y30:AA30" si="31">X30</f>
         <v>1</v>
       </c>
-      <c r="Z30" s="219">
+      <c r="Z30" s="217">
         <f t="shared" si="31"/>
         <v>1</v>
       </c>
-      <c r="AA30" s="219">
+      <c r="AA30" s="217">
         <f t="shared" si="31"/>
         <v>1</v>
       </c>
-      <c r="AB30" s="219">
+      <c r="AB30" s="217">
         <f t="shared" ref="AB30:AF30" si="32">AA30</f>
         <v>1</v>
       </c>
-      <c r="AC30" s="219">
+      <c r="AC30" s="217">
         <f t="shared" si="32"/>
         <v>1</v>
       </c>
-      <c r="AD30" s="219">
+      <c r="AD30" s="217">
         <f t="shared" si="32"/>
         <v>1</v>
       </c>
-      <c r="AE30" s="219">
+      <c r="AE30" s="217">
         <f t="shared" si="32"/>
         <v>1</v>
       </c>
-      <c r="AF30" s="219">
+      <c r="AF30" s="217">
         <f t="shared" si="32"/>
         <v>1</v>
       </c>
@@ -6530,7 +6530,7 @@
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J31" s="265">
+      <c r="J31" s="259">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
@@ -6610,7 +6610,7 @@
       <c r="B32" s="133" t="s">
         <v>339</v>
       </c>
-      <c r="C32" s="227">
+      <c r="C32" s="225">
         <f>IFERROR(RATE(R3-1,0,-C27-W60,C30),0)</f>
         <v>0</v>
       </c>
@@ -6629,7 +6629,7 @@
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J32" s="265">
+      <c r="J32" s="259">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
@@ -6660,46 +6660,46 @@
       <c r="U32" s="93" t="s">
         <v>308</v>
       </c>
-      <c r="V32" s="259">
+      <c r="V32" s="253">
         <v>1</v>
       </c>
-      <c r="W32" s="160">
+      <c r="W32" s="159">
         <f>V32</f>
         <v>1</v>
       </c>
-      <c r="X32" s="160">
+      <c r="X32" s="159">
         <f t="shared" ref="X32:AA32" si="38">W32</f>
         <v>1</v>
       </c>
-      <c r="Y32" s="160">
+      <c r="Y32" s="159">
         <f t="shared" si="38"/>
         <v>1</v>
       </c>
-      <c r="Z32" s="160">
+      <c r="Z32" s="159">
         <f t="shared" si="38"/>
         <v>1</v>
       </c>
-      <c r="AA32" s="160">
+      <c r="AA32" s="159">
         <f t="shared" si="38"/>
         <v>1</v>
       </c>
-      <c r="AB32" s="160">
+      <c r="AB32" s="159">
         <f t="shared" ref="AB32:AF32" si="39">AA32</f>
         <v>1</v>
       </c>
-      <c r="AC32" s="160">
+      <c r="AC32" s="159">
         <f t="shared" si="39"/>
         <v>1</v>
       </c>
-      <c r="AD32" s="160">
+      <c r="AD32" s="159">
         <f t="shared" si="39"/>
         <v>1</v>
       </c>
-      <c r="AE32" s="160">
+      <c r="AE32" s="159">
         <f t="shared" si="39"/>
         <v>1</v>
       </c>
-      <c r="AF32" s="160">
+      <c r="AF32" s="159">
         <f t="shared" si="39"/>
         <v>1</v>
       </c>
@@ -6720,7 +6720,7 @@
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J33" s="265">
+      <c r="J33" s="259">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
@@ -6797,10 +6797,10 @@
       </c>
     </row>
     <row r="34" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="294" t="s">
+      <c r="B34" s="288" t="s">
         <v>123</v>
       </c>
-      <c r="C34" s="295"/>
+      <c r="C34" s="289"/>
       <c r="E34" s="105" t="s">
         <v>62</v>
       </c>
@@ -6816,7 +6816,7 @@
         <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J34" s="163" t="e">
+      <c r="J34" s="162" t="e">
         <f>IF(X19&gt;0,X19,V19)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6844,46 +6844,46 @@
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U34" s="164" t="s">
+      <c r="U34" s="163" t="s">
         <v>310</v>
       </c>
-      <c r="V34" s="164"/>
-      <c r="W34" s="253">
+      <c r="V34" s="163"/>
+      <c r="W34" s="247">
         <v>0.01</v>
       </c>
-      <c r="X34" s="165">
+      <c r="X34" s="164">
         <f>W34</f>
         <v>0.01</v>
       </c>
-      <c r="Y34" s="165">
+      <c r="Y34" s="164">
         <f t="shared" ref="Y34:AA34" si="45">X34</f>
         <v>0.01</v>
       </c>
-      <c r="Z34" s="165">
+      <c r="Z34" s="164">
         <f t="shared" si="45"/>
         <v>0.01</v>
       </c>
-      <c r="AA34" s="165">
+      <c r="AA34" s="164">
         <f t="shared" si="45"/>
         <v>0.01</v>
       </c>
-      <c r="AB34" s="165">
+      <c r="AB34" s="164">
         <f t="shared" ref="AB34:AF34" si="46">AA34</f>
         <v>0.01</v>
       </c>
-      <c r="AC34" s="165">
+      <c r="AC34" s="164">
         <f t="shared" si="46"/>
         <v>0.01</v>
       </c>
-      <c r="AD34" s="165">
+      <c r="AD34" s="164">
         <f t="shared" si="46"/>
         <v>0.01</v>
       </c>
-      <c r="AE34" s="165">
+      <c r="AE34" s="164">
         <f t="shared" si="46"/>
         <v>0.01</v>
       </c>
-      <c r="AF34" s="165">
+      <c r="AF34" s="164">
         <f t="shared" si="46"/>
         <v>0.01</v>
       </c>
@@ -6892,7 +6892,7 @@
       <c r="B35" s="98" t="s">
         <v>328</v>
       </c>
-      <c r="C35" s="156">
+      <c r="C35" s="295">
         <v>0.03</v>
       </c>
       <c r="E35" s="113" t="s">
@@ -6941,46 +6941,46 @@
       <c r="U35" s="127" t="s">
         <v>311</v>
       </c>
-      <c r="V35" s="254">
+      <c r="V35" s="248">
         <v>2.1171800000000001E-2</v>
       </c>
-      <c r="W35" s="167">
+      <c r="W35" s="165">
         <f>V35*(1+W34)</f>
         <v>2.1383518000000001E-2</v>
       </c>
-      <c r="X35" s="167">
+      <c r="X35" s="165">
         <f t="shared" ref="X35:AB35" si="49">W35*(1+X34)</f>
         <v>2.1597353180000001E-2</v>
       </c>
-      <c r="Y35" s="167">
+      <c r="Y35" s="165">
         <f t="shared" si="49"/>
         <v>2.1813326711800002E-2</v>
       </c>
-      <c r="Z35" s="167">
+      <c r="Z35" s="165">
         <f t="shared" si="49"/>
         <v>2.2031459978918002E-2</v>
       </c>
-      <c r="AA35" s="167">
+      <c r="AA35" s="165">
         <f t="shared" si="49"/>
         <v>2.2251774578707181E-2</v>
       </c>
-      <c r="AB35" s="167">
+      <c r="AB35" s="165">
         <f t="shared" si="49"/>
         <v>2.2474292324494254E-2</v>
       </c>
-      <c r="AC35" s="167">
+      <c r="AC35" s="165">
         <f t="shared" ref="AC35" si="50">AB35*(1+AC34)</f>
         <v>2.2699035247739197E-2</v>
       </c>
-      <c r="AD35" s="167">
+      <c r="AD35" s="165">
         <f t="shared" ref="AD35" si="51">AC35*(1+AD34)</f>
         <v>2.2926025600216587E-2</v>
       </c>
-      <c r="AE35" s="167">
+      <c r="AE35" s="165">
         <f t="shared" ref="AE35" si="52">AD35*(1+AE34)</f>
         <v>2.3155285856218753E-2</v>
       </c>
-      <c r="AF35" s="167">
+      <c r="AF35" s="165">
         <f t="shared" ref="AF35" si="53">AE35*(1+AF34)</f>
         <v>2.3386838714780939E-2</v>
       </c>
@@ -6989,69 +6989,69 @@
       <c r="B36" s="98" t="s">
         <v>117</v>
       </c>
-      <c r="C36" s="156">
+      <c r="C36" s="295">
         <v>0.02</v>
       </c>
       <c r="E36" s="123" t="s">
         <v>84</v>
       </c>
-      <c r="F36" s="169"/>
-      <c r="G36" s="170"/>
-      <c r="I36" s="169"/>
-      <c r="J36" s="171" t="e">
+      <c r="F36" s="167"/>
+      <c r="G36" s="168"/>
+      <c r="I36" s="167"/>
+      <c r="J36" s="169" t="e">
         <f>J35/G35-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L36" s="169"/>
-      <c r="M36" s="172"/>
-      <c r="O36" s="169"/>
-      <c r="P36" s="170"/>
-      <c r="R36" s="169"/>
-      <c r="S36" s="170"/>
+      <c r="L36" s="167"/>
+      <c r="M36" s="170"/>
+      <c r="O36" s="167"/>
+      <c r="P36" s="168"/>
+      <c r="R36" s="167"/>
+      <c r="S36" s="168"/>
       <c r="U36" s="152" t="s">
         <v>312</v>
       </c>
-      <c r="V36" s="173">
+      <c r="V36" s="171">
         <f>V33*V35</f>
         <v>1905462</v>
       </c>
-      <c r="W36" s="173">
+      <c r="W36" s="171">
         <f t="shared" ref="W36:AB36" si="54">W33*W35</f>
         <v>1924516.62</v>
       </c>
-      <c r="X36" s="173">
+      <c r="X36" s="171">
         <f t="shared" si="54"/>
         <v>2159735.318</v>
       </c>
-      <c r="Y36" s="173">
+      <c r="Y36" s="171">
         <f t="shared" si="54"/>
         <v>2224959.3246036</v>
       </c>
-      <c r="Z36" s="173">
+      <c r="Z36" s="171">
         <f t="shared" si="54"/>
         <v>2292153.0962066287</v>
       </c>
-      <c r="AA36" s="173">
+      <c r="AA36" s="171">
         <f t="shared" si="54"/>
         <v>2361376.1197120692</v>
       </c>
-      <c r="AB36" s="173">
+      <c r="AB36" s="171">
         <f t="shared" si="54"/>
         <v>2432689.6785273738</v>
       </c>
-      <c r="AC36" s="173">
+      <c r="AC36" s="171">
         <f t="shared" ref="AC36" si="55">AC33*AC35</f>
         <v>2506156.9068189003</v>
       </c>
-      <c r="AD36" s="173">
+      <c r="AD36" s="171">
         <f t="shared" ref="AD36" si="56">AD33*AD35</f>
         <v>2581842.8454048312</v>
       </c>
-      <c r="AE36" s="173">
+      <c r="AE36" s="171">
         <f t="shared" ref="AE36" si="57">AE33*AE35</f>
         <v>2659814.4993360573</v>
       </c>
-      <c r="AF36" s="173">
+      <c r="AF36" s="171">
         <f t="shared" ref="AF36" si="58">AF33*AF35</f>
         <v>2740140.8972160062</v>
       </c>
@@ -7060,7 +7060,7 @@
       <c r="B37" s="112" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="245">
+      <c r="C37" s="296">
         <v>0.03</v>
       </c>
       <c r="E37" s="105" t="s">
@@ -7078,7 +7078,7 @@
         <f>J37*Units</f>
         <v>0</v>
       </c>
-      <c r="J37" s="265">
+      <c r="J37" s="259">
         <f>G37*(1+$C$40)</f>
         <v>0</v>
       </c>
@@ -7106,46 +7106,46 @@
         <f t="shared" ref="S37" si="62">R37/Units</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U37" s="164" t="s">
+      <c r="U37" s="163" t="s">
         <v>313</v>
       </c>
-      <c r="V37" s="164"/>
-      <c r="W37" s="253">
+      <c r="V37" s="163"/>
+      <c r="W37" s="247">
         <v>0.01</v>
       </c>
-      <c r="X37" s="165">
+      <c r="X37" s="164">
         <f>W37</f>
         <v>0.01</v>
       </c>
-      <c r="Y37" s="165">
+      <c r="Y37" s="164">
         <f t="shared" ref="Y37:AF37" si="63">X37</f>
         <v>0.01</v>
       </c>
-      <c r="Z37" s="165">
+      <c r="Z37" s="164">
         <f t="shared" si="63"/>
         <v>0.01</v>
       </c>
-      <c r="AA37" s="165">
+      <c r="AA37" s="164">
         <f t="shared" si="63"/>
         <v>0.01</v>
       </c>
-      <c r="AB37" s="165">
+      <c r="AB37" s="164">
         <f t="shared" si="63"/>
         <v>0.01</v>
       </c>
-      <c r="AC37" s="165">
+      <c r="AC37" s="164">
         <f t="shared" si="63"/>
         <v>0.01</v>
       </c>
-      <c r="AD37" s="165">
+      <c r="AD37" s="164">
         <f t="shared" si="63"/>
         <v>0.01</v>
       </c>
-      <c r="AE37" s="165">
+      <c r="AE37" s="164">
         <f t="shared" si="63"/>
         <v>0.01</v>
       </c>
-      <c r="AF37" s="165">
+      <c r="AF37" s="164">
         <f t="shared" si="63"/>
         <v>0.01</v>
       </c>
@@ -7154,7 +7154,7 @@
       <c r="B38" s="98" t="s">
         <v>118</v>
       </c>
-      <c r="C38" s="156">
+      <c r="C38" s="295">
         <v>0.03</v>
       </c>
       <c r="E38" s="105" t="s">
@@ -7172,7 +7172,7 @@
         <f>J38*I26</f>
         <v>0</v>
       </c>
-      <c r="J38" s="266">
+      <c r="J38" s="260">
         <v>0.02</v>
       </c>
       <c r="L38" s="106" t="e">
@@ -7202,46 +7202,46 @@
       <c r="U38" s="127" t="s">
         <v>314</v>
       </c>
-      <c r="V38" s="255">
+      <c r="V38" s="249">
         <v>50000</v>
       </c>
-      <c r="W38" s="175">
+      <c r="W38" s="173">
         <f>V38*(1+W37)</f>
         <v>50500</v>
       </c>
-      <c r="X38" s="175">
+      <c r="X38" s="173">
         <f t="shared" ref="X38:AB38" si="64">W38*(1+X37)</f>
         <v>51005</v>
       </c>
-      <c r="Y38" s="175">
+      <c r="Y38" s="173">
         <f t="shared" si="64"/>
         <v>51515.05</v>
       </c>
-      <c r="Z38" s="175">
+      <c r="Z38" s="173">
         <f t="shared" si="64"/>
         <v>52030.200500000006</v>
       </c>
-      <c r="AA38" s="175">
+      <c r="AA38" s="173">
         <f t="shared" si="64"/>
         <v>52550.502505000004</v>
       </c>
-      <c r="AB38" s="175">
+      <c r="AB38" s="173">
         <f t="shared" si="64"/>
         <v>53076.007530050003</v>
       </c>
-      <c r="AC38" s="175">
+      <c r="AC38" s="173">
         <f t="shared" ref="AC38" si="65">AB38*(1+AC37)</f>
         <v>53606.767605350506</v>
       </c>
-      <c r="AD38" s="175">
+      <c r="AD38" s="173">
         <f t="shared" ref="AD38" si="66">AC38*(1+AD37)</f>
         <v>54142.835281404012</v>
       </c>
-      <c r="AE38" s="175">
+      <c r="AE38" s="173">
         <f t="shared" ref="AE38" si="67">AD38*(1+AE37)</f>
         <v>54684.263634218056</v>
       </c>
-      <c r="AF38" s="175">
+      <c r="AF38" s="173">
         <f t="shared" ref="AF38" si="68">AE38*(1+AF37)</f>
         <v>55231.106270560238</v>
       </c>
@@ -7250,7 +7250,7 @@
       <c r="B39" s="112" t="s">
         <v>121</v>
       </c>
-      <c r="C39" s="245">
+      <c r="C39" s="296">
         <v>0.03</v>
       </c>
       <c r="E39" s="105" t="s">
@@ -7268,7 +7268,7 @@
         <f>J39*Units</f>
         <v>0</v>
       </c>
-      <c r="J39" s="265">
+      <c r="J39" s="259">
         <f>G39*(1+$C$41)</f>
         <v>0</v>
       </c>
@@ -7296,50 +7296,50 @@
         <f t="shared" ref="S39:S48" si="73">R39/Units</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U39" s="177" t="s">
+      <c r="U39" s="175" t="s">
         <v>315</v>
       </c>
-      <c r="V39" s="178">
+      <c r="V39" s="176">
         <f>SUM(V36,V38)</f>
         <v>1955462</v>
       </c>
-      <c r="W39" s="178">
+      <c r="W39" s="176">
         <f t="shared" ref="W39:AB39" si="74">SUM(W36,W38)</f>
         <v>1975016.62</v>
       </c>
-      <c r="X39" s="178">
+      <c r="X39" s="176">
         <f t="shared" si="74"/>
         <v>2210740.318</v>
       </c>
-      <c r="Y39" s="178">
+      <c r="Y39" s="176">
         <f t="shared" si="74"/>
         <v>2276474.3746035998</v>
       </c>
-      <c r="Z39" s="178">
+      <c r="Z39" s="176">
         <f t="shared" si="74"/>
         <v>2344183.2967066285</v>
       </c>
-      <c r="AA39" s="178">
+      <c r="AA39" s="176">
         <f t="shared" si="74"/>
         <v>2413926.6222170694</v>
       </c>
-      <c r="AB39" s="178">
+      <c r="AB39" s="176">
         <f t="shared" si="74"/>
         <v>2485765.6860574237</v>
       </c>
-      <c r="AC39" s="178">
+      <c r="AC39" s="176">
         <f t="shared" ref="AC39" si="75">SUM(AC36,AC38)</f>
         <v>2559763.6744242506</v>
       </c>
-      <c r="AD39" s="178">
+      <c r="AD39" s="176">
         <f t="shared" ref="AD39" si="76">SUM(AD36,AD38)</f>
         <v>2635985.6806862354</v>
       </c>
-      <c r="AE39" s="178">
+      <c r="AE39" s="176">
         <f t="shared" ref="AE39" si="77">SUM(AE36,AE38)</f>
         <v>2714498.7629702752</v>
       </c>
-      <c r="AF39" s="178">
+      <c r="AF39" s="176">
         <f t="shared" ref="AF39" si="78">SUM(AF36,AF38)</f>
         <v>2795372.0034865662</v>
       </c>
@@ -7348,7 +7348,7 @@
       <c r="B40" s="98" t="s">
         <v>119</v>
       </c>
-      <c r="C40" s="246">
+      <c r="C40" s="297">
         <v>0.02</v>
       </c>
       <c r="E40" s="105" t="s">
@@ -7366,7 +7366,7 @@
         <f>J40*Units</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J40" s="163" t="e">
+      <c r="J40" s="162" t="e">
         <f>Y25/Units</f>
         <v>#DIV/0!</v>
       </c>
@@ -7397,46 +7397,46 @@
       <c r="U40" s="127" t="s">
         <v>316</v>
       </c>
-      <c r="V40" s="256">
-        <v>0</v>
-      </c>
-      <c r="W40" s="180">
+      <c r="V40" s="250">
+        <v>0</v>
+      </c>
+      <c r="W40" s="178">
         <f>V40</f>
         <v>0</v>
       </c>
-      <c r="X40" s="180">
+      <c r="X40" s="178">
         <f t="shared" ref="X40:AA40" si="79">W40</f>
         <v>0</v>
       </c>
-      <c r="Y40" s="180">
+      <c r="Y40" s="178">
         <f t="shared" si="79"/>
         <v>0</v>
       </c>
-      <c r="Z40" s="180">
+      <c r="Z40" s="178">
         <f t="shared" si="79"/>
         <v>0</v>
       </c>
-      <c r="AA40" s="180">
+      <c r="AA40" s="178">
         <f t="shared" si="79"/>
         <v>0</v>
       </c>
-      <c r="AB40" s="180">
+      <c r="AB40" s="178">
         <f t="shared" ref="AB40:AF40" si="80">AA40</f>
         <v>0</v>
       </c>
-      <c r="AC40" s="180">
+      <c r="AC40" s="178">
         <f t="shared" si="80"/>
         <v>0</v>
       </c>
-      <c r="AD40" s="180">
+      <c r="AD40" s="178">
         <f t="shared" si="80"/>
         <v>0</v>
       </c>
-      <c r="AE40" s="180">
+      <c r="AE40" s="178">
         <f t="shared" si="80"/>
         <v>0</v>
       </c>
-      <c r="AF40" s="180">
+      <c r="AF40" s="178">
         <f t="shared" si="80"/>
         <v>0</v>
       </c>
@@ -7445,7 +7445,7 @@
       <c r="B41" s="133" t="s">
         <v>120</v>
       </c>
-      <c r="C41" s="166">
+      <c r="C41" s="298">
         <v>0.02</v>
       </c>
       <c r="E41" s="105" t="s">
@@ -7463,7 +7463,7 @@
         <f>J41*Units</f>
         <v>0</v>
       </c>
-      <c r="J41" s="265">
+      <c r="J41" s="259">
         <f>G41*(1+$C$40)</f>
         <v>0</v>
       </c>
@@ -7491,56 +7491,56 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U41" s="177" t="s">
+      <c r="U41" s="175" t="s">
         <v>317</v>
       </c>
-      <c r="V41" s="178">
+      <c r="V41" s="176">
         <f t="shared" ref="V41:AB41" si="81">V39*(1-V40)</f>
         <v>1955462</v>
       </c>
-      <c r="W41" s="178">
+      <c r="W41" s="176">
         <f t="shared" si="81"/>
         <v>1975016.62</v>
       </c>
-      <c r="X41" s="178">
+      <c r="X41" s="176">
         <f t="shared" si="81"/>
         <v>2210740.318</v>
       </c>
-      <c r="Y41" s="178">
+      <c r="Y41" s="176">
         <f t="shared" si="81"/>
         <v>2276474.3746035998</v>
       </c>
-      <c r="Z41" s="178">
+      <c r="Z41" s="176">
         <f t="shared" si="81"/>
         <v>2344183.2967066285</v>
       </c>
-      <c r="AA41" s="178">
+      <c r="AA41" s="176">
         <f t="shared" si="81"/>
         <v>2413926.6222170694</v>
       </c>
-      <c r="AB41" s="178">
+      <c r="AB41" s="176">
         <f t="shared" si="81"/>
         <v>2485765.6860574237</v>
       </c>
-      <c r="AC41" s="178">
+      <c r="AC41" s="176">
         <f t="shared" ref="AC41:AF41" si="82">AC39*(1-AC40)</f>
         <v>2559763.6744242506</v>
       </c>
-      <c r="AD41" s="178">
+      <c r="AD41" s="176">
         <f t="shared" si="82"/>
         <v>2635985.6806862354</v>
       </c>
-      <c r="AE41" s="178">
+      <c r="AE41" s="176">
         <f t="shared" si="82"/>
         <v>2714498.7629702752</v>
       </c>
-      <c r="AF41" s="178">
+      <c r="AF41" s="176">
         <f t="shared" si="82"/>
         <v>2795372.0034865662</v>
       </c>
     </row>
     <row r="42" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C42" s="168"/>
+      <c r="C42" s="166"/>
       <c r="E42" s="113" t="s">
         <v>83</v>
       </c>
@@ -7584,44 +7584,44 @@
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V42" s="183"/>
-      <c r="W42" s="220">
+      <c r="V42" s="181"/>
+      <c r="W42" s="218">
         <f>W41/V41-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="X42" s="220">
+      <c r="X42" s="218">
         <f t="shared" ref="X42:AB42" si="85">X41/W41-1</f>
         <v>0.11935276676304629</v>
       </c>
-      <c r="Y42" s="220">
+      <c r="Y42" s="218">
         <f t="shared" si="85"/>
         <v>2.9733956570289433E-2</v>
       </c>
-      <c r="Z42" s="220">
+      <c r="Z42" s="218">
         <f t="shared" si="85"/>
         <v>2.9742887887687752E-2</v>
       </c>
-      <c r="AA42" s="220">
+      <c r="AA42" s="218">
         <f t="shared" si="85"/>
         <v>2.9751651932860446E-2</v>
       </c>
-      <c r="AB42" s="220">
+      <c r="AB42" s="218">
         <f t="shared" si="85"/>
         <v>2.9760251690821304E-2</v>
       </c>
-      <c r="AC42" s="220">
+      <c r="AC42" s="218">
         <f t="shared" ref="AC42" si="86">AC41/AB41-1</f>
         <v>2.9768690098941786E-2</v>
       </c>
-      <c r="AD42" s="220">
+      <c r="AD42" s="218">
         <f t="shared" ref="AD42" si="87">AD41/AC41-1</f>
         <v>2.9776970047490359E-2</v>
       </c>
-      <c r="AE42" s="220">
+      <c r="AE42" s="218">
         <f t="shared" ref="AE42" si="88">AE41/AD41-1</f>
         <v>2.9785094380178956E-2</v>
       </c>
-      <c r="AF42" s="220">
+      <c r="AF42" s="218">
         <f t="shared" ref="AF42" si="89">AF41/AE41-1</f>
         <v>2.97930658947132E-2</v>
       </c>
@@ -7630,7 +7630,7 @@
       <c r="B43" s="95" t="s">
         <v>344</v>
       </c>
-      <c r="C43" s="174">
+      <c r="C43" s="172">
         <f>IF(SUM(C44,C49,C54)=C14,C14,"REVIEW")</f>
         <v>0</v>
       </c>
@@ -7649,7 +7649,7 @@
         <f>IFERROR('T12 Clean'!O41,0)</f>
         <v>0</v>
       </c>
-      <c r="J43" s="265">
+      <c r="J43" s="259">
         <f>G43*(1+$C$40)</f>
         <v>0</v>
       </c>
@@ -7677,55 +7677,55 @@
         <f t="shared" ref="S43" si="91">R43/Units</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U43" s="184" t="s">
+      <c r="U43" s="182" t="s">
         <v>319</v>
       </c>
-      <c r="V43" s="184">
-        <v>0</v>
-      </c>
-      <c r="W43" s="184">
+      <c r="V43" s="182">
+        <v>0</v>
+      </c>
+      <c r="W43" s="182">
         <f>V43+1</f>
         <v>1</v>
       </c>
-      <c r="X43" s="184">
+      <c r="X43" s="182">
         <f t="shared" ref="X43:AB43" si="92">W43+1</f>
         <v>2</v>
       </c>
-      <c r="Y43" s="184">
+      <c r="Y43" s="182">
         <f t="shared" si="92"/>
         <v>3</v>
       </c>
-      <c r="Z43" s="184">
+      <c r="Z43" s="182">
         <f t="shared" si="92"/>
         <v>4</v>
       </c>
-      <c r="AA43" s="184">
+      <c r="AA43" s="182">
         <f t="shared" si="92"/>
         <v>5</v>
       </c>
-      <c r="AB43" s="184">
+      <c r="AB43" s="182">
         <f t="shared" si="92"/>
         <v>6</v>
       </c>
-      <c r="AC43" s="184">
+      <c r="AC43" s="182">
         <f t="shared" ref="AC43:AE43" si="93">AB43+1</f>
         <v>7</v>
       </c>
-      <c r="AD43" s="184">
+      <c r="AD43" s="182">
         <f t="shared" si="93"/>
         <v>8</v>
       </c>
-      <c r="AE43" s="184">
+      <c r="AE43" s="182">
         <f t="shared" si="93"/>
         <v>9</v>
       </c>
-      <c r="AF43" s="184"/>
+      <c r="AF43" s="182"/>
     </row>
     <row r="44" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="247" t="s">
+      <c r="B44" s="241" t="s">
         <v>264</v>
       </c>
-      <c r="C44" s="239">
+      <c r="C44" s="237">
         <f>C14</f>
         <v>0</v>
       </c>
@@ -7818,13 +7818,13 @@
       <c r="AF44" s="146"/>
     </row>
     <row r="45" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="176" t="s">
+      <c r="B45" s="174" t="s">
         <v>265</v>
       </c>
-      <c r="C45" s="248">
+      <c r="C45" s="242">
         <v>75</v>
       </c>
-      <c r="E45" s="185"/>
+      <c r="E45" s="183"/>
       <c r="F45" s="106"/>
       <c r="G45" s="107"/>
       <c r="I45" s="106"/>
@@ -7842,144 +7842,144 @@
         <f ca="1">EOMONTH(V25,-12)</f>
         <v>46234</v>
       </c>
-      <c r="W45" s="186">
+      <c r="W45" s="184">
         <f ca="1">EOMONTH(V45,12)</f>
         <v>46599</v>
       </c>
-      <c r="X45" s="186">
+      <c r="X45" s="184">
         <f t="shared" ref="X45:AB45" ca="1" si="96">EOMONTH(W45,12)</f>
         <v>46965</v>
       </c>
-      <c r="Y45" s="186">
+      <c r="Y45" s="184">
         <f t="shared" ca="1" si="96"/>
         <v>47330</v>
       </c>
-      <c r="Z45" s="186">
+      <c r="Z45" s="184">
         <f t="shared" ca="1" si="96"/>
         <v>47695</v>
       </c>
-      <c r="AA45" s="186">
+      <c r="AA45" s="184">
         <f t="shared" ca="1" si="96"/>
         <v>48060</v>
       </c>
-      <c r="AB45" s="186">
+      <c r="AB45" s="184">
         <f t="shared" ca="1" si="96"/>
         <v>48426</v>
       </c>
-      <c r="AC45" s="186">
+      <c r="AC45" s="184">
         <f t="shared" ref="AC45:AE45" ca="1" si="97">EOMONTH(AB45,12)</f>
         <v>48791</v>
       </c>
-      <c r="AD45" s="186">
+      <c r="AD45" s="184">
         <f t="shared" ca="1" si="97"/>
         <v>49156</v>
       </c>
-      <c r="AE45" s="186">
+      <c r="AE45" s="184">
         <f t="shared" ca="1" si="97"/>
         <v>49521</v>
       </c>
       <c r="AF45" s="146"/>
     </row>
     <row r="46" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="179" t="s">
+      <c r="B46" s="177" t="s">
         <v>266</v>
       </c>
-      <c r="C46" s="249">
-        <v>0</v>
-      </c>
-      <c r="E46" s="187" t="s">
+      <c r="C46" s="243">
+        <v>0</v>
+      </c>
+      <c r="E46" s="185" t="s">
         <v>351</v>
       </c>
-      <c r="F46" s="188">
+      <c r="F46" s="186">
         <f>F26-F44</f>
         <v>0</v>
       </c>
-      <c r="G46" s="189">
+      <c r="G46" s="187">
         <f>IFERROR(F46/Units,0)</f>
         <v>0</v>
       </c>
-      <c r="I46" s="188" t="e">
+      <c r="I46" s="186" t="e">
         <f>I26-I44</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J46" s="189">
+      <c r="J46" s="187">
         <f>IFERROR(I46/Units,0)</f>
         <v>0</v>
       </c>
-      <c r="L46" s="188" t="e">
+      <c r="L46" s="186" t="e">
         <f>L26-L44</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M46" s="190" t="e">
+      <c r="M46" s="188" t="e">
         <f>L46/Units</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O46" s="188" t="e">
+      <c r="O46" s="186" t="e">
         <f>O26-O44</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P46" s="189" t="e">
+      <c r="P46" s="187" t="e">
         <f t="shared" ref="P46" si="98">O46/Units</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R46" s="188" t="e">
+      <c r="R46" s="186" t="e">
         <f>R26-R44</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S46" s="189" t="e">
+      <c r="S46" s="187" t="e">
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U46" s="177" t="s">
+      <c r="U46" s="175" t="s">
         <v>321</v>
       </c>
-      <c r="V46" s="178">
+      <c r="V46" s="176">
         <f ca="1">IF(YEAR(V45)=YEAR(V44),V41,(((12-MONTH(V45))*V41)+(MONTH(V45)*W41))/12)</f>
         <v>1966868.8616666666</v>
       </c>
-      <c r="W46" s="178">
+      <c r="W46" s="176">
         <f t="shared" ref="W46:AB46" ca="1" si="99">IF(YEAR(W45)=YEAR(W44),W41,(((12-MONTH(W45))*W41)+(MONTH(W45)*X41))/12)</f>
         <v>2112522.1105</v>
       </c>
-      <c r="X46" s="178">
+      <c r="X46" s="176">
         <f t="shared" ca="1" si="99"/>
         <v>2249085.1843520999</v>
       </c>
-      <c r="Y46" s="178">
+      <c r="Y46" s="176">
         <f t="shared" ca="1" si="99"/>
         <v>2315971.2458303664</v>
       </c>
-      <c r="Z46" s="178">
+      <c r="Z46" s="176">
         <f t="shared" ca="1" si="99"/>
         <v>2384866.9032543856</v>
       </c>
-      <c r="AA46" s="178">
+      <c r="AA46" s="176">
         <f t="shared" ca="1" si="99"/>
         <v>2455832.7427906096</v>
       </c>
-      <c r="AB46" s="178">
+      <c r="AB46" s="176">
         <f t="shared" ca="1" si="99"/>
         <v>2528931.179271406</v>
       </c>
-      <c r="AC46" s="178">
+      <c r="AC46" s="176">
         <f t="shared" ref="AC46" ca="1" si="100">IF(YEAR(AC45)=YEAR(AC44),AC41,(((12-MONTH(AC45))*AC41)+(MONTH(AC45)*AD41))/12)</f>
         <v>2604226.5114104082</v>
       </c>
-      <c r="AD46" s="178">
+      <c r="AD46" s="176">
         <f t="shared" ref="AD46" ca="1" si="101">IF(YEAR(AD45)=YEAR(AD44),AD41,(((12-MONTH(AD45))*AD41)+(MONTH(AD45)*AE41))/12)</f>
         <v>2681784.9786852584</v>
       </c>
-      <c r="AE46" s="178">
+      <c r="AE46" s="176">
         <f t="shared" ref="AE46" ca="1" si="102">IF(YEAR(AE45)=YEAR(AE44),AE41,(((12-MONTH(AE45))*AE41)+(MONTH(AE45)*AF41))/12)</f>
         <v>2761674.8199381116</v>
       </c>
-      <c r="AF46" s="173"/>
+      <c r="AF46" s="171"/>
     </row>
     <row r="47" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B47" s="145" t="s">
         <v>267</v>
       </c>
-      <c r="C47" s="181">
+      <c r="C47" s="179">
         <f>C44*C45*C46*12</f>
         <v>0</v>
       </c>
@@ -7998,7 +7998,7 @@
         <f>J47*Units</f>
         <v>0</v>
       </c>
-      <c r="J47" s="265">
+      <c r="J47" s="259">
         <v>300</v>
       </c>
       <c r="L47" s="106">
@@ -8025,102 +8025,102 @@
         <f>P47+50</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="W47" s="220">
+      <c r="W47" s="218">
         <f ca="1">W46/V46-1</f>
         <v>7.4053360481751263E-2</v>
       </c>
-      <c r="X47" s="220">
+      <c r="X47" s="218">
         <f t="shared" ref="X47" ca="1" si="104">X46/W46-1</f>
         <v>6.4644565457247616E-2</v>
       </c>
-      <c r="Y47" s="220">
+      <c r="Y47" s="218">
         <f t="shared" ref="Y47" ca="1" si="105">Y46/X46-1</f>
         <v>2.9739229951636803E-2</v>
       </c>
-      <c r="Z47" s="220">
+      <c r="Z47" s="218">
         <f t="shared" ref="Z47" ca="1" si="106">Z46/Y46-1</f>
         <v>2.9748062523685448E-2</v>
       </c>
-      <c r="AA47" s="220">
+      <c r="AA47" s="218">
         <f t="shared" ref="AA47" ca="1" si="107">AA46/Z46-1</f>
         <v>2.975672958494413E-2</v>
       </c>
-      <c r="AB47" s="220">
+      <c r="AB47" s="218">
         <f t="shared" ref="AB47" ca="1" si="108">AB46/AA46-1</f>
         <v>2.976523409234022E-2</v>
       </c>
-      <c r="AC47" s="220">
+      <c r="AC47" s="218">
         <f t="shared" ref="AC47" ca="1" si="109">AC46/AB46-1</f>
         <v>2.9773578955476054E-2</v>
       </c>
-      <c r="AD47" s="220">
+      <c r="AD47" s="218">
         <f t="shared" ref="AD47" ca="1" si="110">AD46/AC46-1</f>
         <v>2.9781767037171392E-2</v>
       </c>
-      <c r="AE47" s="220">
+      <c r="AE47" s="218">
         <f t="shared" ref="AE47" ca="1" si="111">AE46/AD46-1</f>
         <v>2.9789801154013196E-2</v>
       </c>
-      <c r="AF47" s="191"/>
+      <c r="AF47" s="189"/>
     </row>
     <row r="48" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B48" s="98"/>
-      <c r="C48" s="182"/>
-      <c r="E48" s="192" t="s">
+      <c r="C48" s="180"/>
+      <c r="E48" s="190" t="s">
         <v>352</v>
       </c>
-      <c r="F48" s="193">
+      <c r="F48" s="191">
         <f>F46-F47</f>
         <v>0</v>
       </c>
-      <c r="G48" s="194">
+      <c r="G48" s="192">
         <f>IFERROR(F48/Units,0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="193" t="e">
+      <c r="I48" s="191" t="e">
         <f>I46-I47</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J48" s="194">
+      <c r="J48" s="192">
         <f>IFERROR(I48/Units,0)</f>
         <v>0</v>
       </c>
-      <c r="L48" s="193" t="e">
+      <c r="L48" s="191" t="e">
         <f>L46-L47</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M48" s="195" t="e">
+      <c r="M48" s="193" t="e">
         <f>L48/Units</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O48" s="193" t="e">
+      <c r="O48" s="191" t="e">
         <f>O46-O47</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P48" s="194" t="e">
+      <c r="P48" s="192" t="e">
         <f t="shared" ref="P48" si="112">O48/Units</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R48" s="193" t="e">
+      <c r="R48" s="191" t="e">
         <f>R46-R47</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S48" s="194" t="e">
+      <c r="S48" s="192" t="e">
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z48" s="196"/>
-      <c r="AA48" s="196"/>
+      <c r="Z48" s="194"/>
+      <c r="AA48" s="194"/>
       <c r="AB48" s="146"/>
     </row>
     <row r="49" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="271" t="s">
+      <c r="B49" s="265" t="s">
         <v>264</v>
       </c>
-      <c r="C49" s="272">
-        <v>0</v>
-      </c>
-      <c r="R49" s="226"/>
+      <c r="C49" s="266">
+        <v>0</v>
+      </c>
+      <c r="R49" s="224"/>
       <c r="U49" s="95" t="s">
         <v>298</v>
       </c>
@@ -8136,154 +8136,154 @@
       <c r="Y49" s="97" t="s">
         <v>294</v>
       </c>
-      <c r="Z49" s="196"/>
-      <c r="AA49" s="196"/>
+      <c r="Z49" s="194"/>
+      <c r="AA49" s="194"/>
       <c r="AB49" s="146"/>
     </row>
     <row r="50" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B50" s="98" t="s">
         <v>265</v>
       </c>
-      <c r="C50" s="273">
-        <v>0</v>
-      </c>
-      <c r="I50" s="197"/>
-      <c r="J50" s="197"/>
+      <c r="C50" s="267">
+        <v>0</v>
+      </c>
+      <c r="I50" s="195"/>
+      <c r="J50" s="195"/>
       <c r="U50" s="98" t="s">
         <v>290</v>
       </c>
-      <c r="V50" s="260">
+      <c r="V50" s="254">
         <f>Units</f>
         <v>0</v>
       </c>
-      <c r="W50" s="222">
-        <v>0</v>
-      </c>
-      <c r="X50" s="222">
-        <v>0</v>
-      </c>
-      <c r="Y50" s="198">
+      <c r="W50" s="220">
+        <v>0</v>
+      </c>
+      <c r="X50" s="220">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="196">
         <f>MIN(SUM(V50:X50),Units)</f>
         <v>0</v>
       </c>
-      <c r="Z50" s="173"/>
-      <c r="AA50" s="173"/>
-      <c r="AB50" s="173"/>
+      <c r="Z50" s="171"/>
+      <c r="AA50" s="171"/>
+      <c r="AB50" s="171"/>
     </row>
     <row r="51" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="274" t="s">
+      <c r="B51" s="268" t="s">
         <v>266</v>
       </c>
-      <c r="C51" s="225">
-        <v>0</v>
-      </c>
-      <c r="I51" s="199"/>
-      <c r="J51" s="199"/>
+      <c r="C51" s="223">
+        <v>0</v>
+      </c>
+      <c r="I51" s="197"/>
+      <c r="J51" s="197"/>
       <c r="U51" s="98" t="s">
         <v>295</v>
       </c>
-      <c r="V51" s="261">
-        <v>0</v>
-      </c>
-      <c r="W51" s="223">
-        <v>0</v>
-      </c>
-      <c r="X51" s="223">
-        <v>0</v>
-      </c>
-      <c r="Y51" s="200" t="e">
+      <c r="V51" s="255">
+        <v>0</v>
+      </c>
+      <c r="W51" s="221">
+        <v>0</v>
+      </c>
+      <c r="X51" s="221">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="198" t="e">
         <f>SUMPRODUCT(V50:X50,V51:X51)/Y50</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="52" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="217" t="s">
+      <c r="B52" s="215" t="s">
         <v>267</v>
       </c>
-      <c r="C52" s="275">
+      <c r="C52" s="269">
         <f>C49*C50*C51*12</f>
         <v>0</v>
       </c>
       <c r="U52" s="133" t="s">
         <v>329</v>
       </c>
-      <c r="V52" s="262">
-        <v>0</v>
-      </c>
-      <c r="W52" s="224">
-        <v>0</v>
-      </c>
-      <c r="X52" s="224">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="201" t="e">
+      <c r="V52" s="256">
+        <v>0</v>
+      </c>
+      <c r="W52" s="222">
+        <v>0</v>
+      </c>
+      <c r="X52" s="222">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="199" t="e">
         <f>SUMPRODUCT(V50:X50,V52:X52)/Y50</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="53" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="276"/>
-      <c r="C53" s="277"/>
-      <c r="U53" s="204" t="s">
+      <c r="B53" s="270"/>
+      <c r="C53" s="271"/>
+      <c r="U53" s="202" t="s">
         <v>330</v>
       </c>
-      <c r="V53" s="205">
+      <c r="V53" s="203">
         <f>IFERROR(V51*12/V52,0)</f>
         <v>0</v>
       </c>
-      <c r="W53" s="205">
+      <c r="W53" s="203">
         <f>IFERROR(W51*12/W52,0)</f>
         <v>0</v>
       </c>
-      <c r="X53" s="206">
+      <c r="X53" s="204">
         <f>IFERROR(X51*12/X52,0)</f>
         <v>0</v>
       </c>
-      <c r="Y53" s="207">
+      <c r="Y53" s="205">
         <f>IFERROR(Y51*12/Y52,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="271" t="s">
+      <c r="B54" s="265" t="s">
         <v>264</v>
       </c>
-      <c r="C54" s="272">
-        <v>0</v>
-      </c>
-      <c r="Y54" s="210"/>
+      <c r="C54" s="266">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="208"/>
     </row>
     <row r="55" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B55" s="98" t="s">
         <v>265</v>
       </c>
-      <c r="C55" s="273">
-        <v>0</v>
-      </c>
-      <c r="U55" s="294" t="s">
+      <c r="C55" s="267">
+        <v>0</v>
+      </c>
+      <c r="U55" s="288" t="s">
         <v>332</v>
       </c>
-      <c r="V55" s="296"/>
-      <c r="W55" s="295"/>
+      <c r="V55" s="290"/>
+      <c r="W55" s="289"/>
       <c r="X55" s="93" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="56" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="274" t="s">
+      <c r="B56" s="268" t="s">
         <v>266</v>
       </c>
-      <c r="C56" s="225">
+      <c r="C56" s="223">
         <v>0</v>
       </c>
       <c r="U56" s="98" t="s">
         <v>343</v>
       </c>
-      <c r="W56" s="211" t="e">
+      <c r="W56" s="209" t="e">
         <f>Y50*Y52</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X56" s="282">
+      <c r="X56" s="276">
         <f>IFERROR(($Y$51*$Y$50*12)/(W56*(1+$V$59)),0)</f>
         <v>0</v>
       </c>
@@ -8292,69 +8292,69 @@
       <c r="B57" s="145" t="s">
         <v>267</v>
       </c>
-      <c r="C57" s="181">
+      <c r="C57" s="179">
         <f>C54*C55*C56*12</f>
         <v>0</v>
       </c>
       <c r="U57" s="98" t="s">
         <v>333</v>
       </c>
-      <c r="W57" s="263">
+      <c r="W57" s="257">
         <v>1500000</v>
       </c>
-      <c r="X57" s="282">
+      <c r="X57" s="276">
         <f>IFERROR(($Y$51*$Y$50*12)/(SUM(W56:W57)*(1+$V$59)),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B58" s="98"/>
-      <c r="C58" s="182"/>
+      <c r="C58" s="180"/>
       <c r="U58" s="112" t="s">
         <v>353</v>
       </c>
-      <c r="V58" s="212"/>
-      <c r="W58" s="264">
+      <c r="V58" s="210"/>
+      <c r="W58" s="258">
         <v>500000</v>
       </c>
-      <c r="X58" s="282"/>
+      <c r="X58" s="276"/>
     </row>
     <row r="59" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="202" t="s">
+      <c r="B59" s="200" t="s">
         <v>269</v>
       </c>
-      <c r="C59" s="203">
+      <c r="C59" s="201">
         <f>IF(C47=0,F18*(1+$C$38),SUM(C47,C52,C57))</f>
         <v>0</v>
       </c>
       <c r="U59" s="133" t="s">
         <v>334</v>
       </c>
-      <c r="V59" s="213">
+      <c r="V59" s="211">
         <v>0.05</v>
       </c>
-      <c r="W59" s="214" t="e">
+      <c r="W59" s="212" t="e">
         <f>V59*SUM(W56,W57)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="60" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="208" t="s">
+      <c r="B60" s="206" t="s">
         <v>270</v>
       </c>
-      <c r="C60" s="209" t="e">
+      <c r="C60" s="207" t="e">
         <f>C59/F18-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U60" s="215" t="s">
+      <c r="U60" s="213" t="s">
         <v>335</v>
       </c>
       <c r="V60" s="155"/>
-      <c r="W60" s="216" t="e">
+      <c r="W60" s="214" t="e">
         <f>SUM(W56:W59)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X60" s="282">
+      <c r="X60" s="276">
         <f>IFERROR(($Y$51*$Y$50*12)/W60,0)</f>
         <v>0</v>
       </c>
@@ -8565,23 +8565,23 @@
       </c>
     </row>
     <row r="3" spans="2:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="299" t="str">
+      <c r="B3" s="293" t="str">
         <f>CONCATENATE('QuickVal Proforma'!C5," | ","T12")</f>
         <v xml:space="preserve"> | T12</v>
       </c>
-      <c r="C3" s="299"/>
-      <c r="D3" s="299"/>
-      <c r="E3" s="299"/>
-      <c r="F3" s="299"/>
-      <c r="G3" s="299"/>
-      <c r="H3" s="299"/>
-      <c r="I3" s="299"/>
-      <c r="J3" s="299"/>
-      <c r="K3" s="299"/>
-      <c r="L3" s="299"/>
-      <c r="M3" s="299"/>
-      <c r="N3" s="299"/>
-      <c r="O3" s="299"/>
+      <c r="C3" s="293"/>
+      <c r="D3" s="293"/>
+      <c r="E3" s="293"/>
+      <c r="F3" s="293"/>
+      <c r="G3" s="293"/>
+      <c r="H3" s="293"/>
+      <c r="I3" s="293"/>
+      <c r="J3" s="293"/>
+      <c r="K3" s="293"/>
+      <c r="L3" s="293"/>
+      <c r="M3" s="293"/>
+      <c r="N3" s="293"/>
+      <c r="O3" s="293"/>
     </row>
     <row r="4" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="51" t="s">
@@ -9204,7 +9204,7 @@
       <c r="B13" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="281">
+      <c r="C13" s="275">
         <f>SUMIF('T12 Intake'!$Q$4:$Q$1000,$B13,'T12 Intake'!D$4:D$1000)</f>
         <v>0</v>
       </c>
@@ -9708,7 +9708,7 @@
       <c r="B21" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="281">
+      <c r="C21" s="275">
         <f>SUMIF('T12 Intake'!$Q$4:$Q$1000,$B21,'T12 Intake'!D$4:D$1000)</f>
         <v>0</v>
       </c>
@@ -12044,28 +12044,28 @@
     </row>
     <row r="2" spans="1:20" s="3" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="300" t="str">
+      <c r="B2" s="294" t="str">
         <f>CONCATENATE('QuickVal Proforma'!C5," | ","T12 Intake")</f>
         <v xml:space="preserve"> | T12 Intake</v>
       </c>
-      <c r="C2" s="300"/>
-      <c r="D2" s="300"/>
-      <c r="E2" s="300"/>
-      <c r="F2" s="300"/>
-      <c r="G2" s="300"/>
-      <c r="H2" s="300"/>
-      <c r="I2" s="300"/>
-      <c r="J2" s="300"/>
-      <c r="K2" s="300"/>
-      <c r="L2" s="300"/>
-      <c r="M2" s="300"/>
-      <c r="N2" s="300"/>
-      <c r="O2" s="300"/>
-      <c r="P2" s="300"/>
-      <c r="Q2" s="300"/>
-      <c r="R2" s="300"/>
-      <c r="S2" s="300"/>
-      <c r="T2" s="300"/>
+      <c r="C2" s="294"/>
+      <c r="D2" s="294"/>
+      <c r="E2" s="294"/>
+      <c r="F2" s="294"/>
+      <c r="G2" s="294"/>
+      <c r="H2" s="294"/>
+      <c r="I2" s="294"/>
+      <c r="J2" s="294"/>
+      <c r="K2" s="294"/>
+      <c r="L2" s="294"/>
+      <c r="M2" s="294"/>
+      <c r="N2" s="294"/>
+      <c r="O2" s="294"/>
+      <c r="P2" s="294"/>
+      <c r="Q2" s="294"/>
+      <c r="R2" s="294"/>
+      <c r="S2" s="294"/>
+      <c r="T2" s="294"/>
     </row>
     <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1"/>
@@ -12119,7 +12119,7 @@
         <f>EOMONTH(O3,-1)</f>
         <v>45838</v>
       </c>
-      <c r="O3" s="278">
+      <c r="O3" s="272">
         <v>45869</v>
       </c>
       <c r="P3" s="7" t="s">
@@ -13082,7 +13082,7 @@
       <c r="P40" s="24"/>
       <c r="Q40" s="25"/>
       <c r="R40" s="16"/>
-      <c r="S40" s="279"/>
+      <c r="S40" s="273"/>
     </row>
     <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="1"/>
